--- a/data/gcse-subject-tracker.xlsx
+++ b/data/gcse-subject-tracker.xlsx
@@ -32,7 +32,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Health &amp; Social Care'!$A$1:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Hospitality &amp; Catering'!$A$1:$H$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Music Technology'!$A$1:$H$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Business Studies'!$A$1:$H$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Business Studies'!$A$1:$H$91</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -12169,7 +12169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H61"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -14144,8 +14144,968 @@
       <c r="G61" s="2" t="inlineStr"/>
       <c r="H61" s="2" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" s="12" t="inlineStr">
+        <is>
+          <t>Enterprise, Entrepreneurs &amp; Risk and Reward</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="12" t="inlineStr">
+        <is>
+          <t>Business Planning</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="12" t="inlineStr">
+        <is>
+          <t>Business Ownership &amp; Limited Liability</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E65" s="12" t="inlineStr">
+        <is>
+          <t>Business Aims &amp; Objectives</t>
+        </is>
+      </c>
+      <c r="F65" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E66" s="12" t="inlineStr">
+        <is>
+          <t>Stakeholders in Business</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>Business Growth</t>
+        </is>
+      </c>
+      <c r="F67" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>Role &amp; Purpose of Marketing</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E69" s="12" t="inlineStr">
+        <is>
+          <t>Market Research</t>
+        </is>
+      </c>
+      <c r="F69" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E70" s="12" t="inlineStr">
+        <is>
+          <t>Market Segmentation</t>
+        </is>
+      </c>
+      <c r="F70" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" s="12" t="inlineStr">
+        <is>
+          <t>Product &amp; the Product Life Cycle</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E72" s="12" t="inlineStr">
+        <is>
+          <t>Pricing Methods</t>
+        </is>
+      </c>
+      <c r="F72" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E73" s="12" t="inlineStr">
+        <is>
+          <t>Promotion &amp; Place</t>
+        </is>
+      </c>
+      <c r="F73" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E74" s="12" t="inlineStr">
+        <is>
+          <t>The Marketing Mix in Action</t>
+        </is>
+      </c>
+      <c r="F74" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E75" s="12" t="inlineStr">
+        <is>
+          <t>Organisational Structures &amp; Ways of Working</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Business Activity, Marketing &amp; People</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E76" s="12" t="inlineStr">
+        <is>
+          <t>Recruitment, Motivation, Training &amp; Employment Law</t>
+        </is>
+      </c>
+      <c r="F76" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E77" s="12" t="inlineStr">
+        <is>
+          <t>Production Processes &amp; Technology</t>
+        </is>
+      </c>
+      <c r="F77" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="12" t="inlineStr">
+        <is>
+          <t>Quality of Goods &amp; Services</t>
+        </is>
+      </c>
+      <c r="F78" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" s="12" t="inlineStr">
+        <is>
+          <t>The Sales Process &amp; Customer Service</t>
+        </is>
+      </c>
+      <c r="F79" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E80" s="12" t="inlineStr">
+        <is>
+          <t>Consumer Law</t>
+        </is>
+      </c>
+      <c r="F80" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E81" s="12" t="inlineStr">
+        <is>
+          <t>Business Location</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="12" t="inlineStr">
+        <is>
+          <t>Working with Suppliers &amp; Procurement</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E83" s="12" t="inlineStr">
+        <is>
+          <t>The Role of the Finance Function</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E84" s="12" t="inlineStr">
+        <is>
+          <t>Sources of Finance</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" s="12" t="inlineStr">
+        <is>
+          <t>Revenue, Costs &amp; Profit</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" s="12" t="inlineStr">
+        <is>
+          <t>Profit Margins &amp; Average Rate of Return</t>
+        </is>
+      </c>
+      <c r="F86" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E87" s="12" t="inlineStr">
+        <is>
+          <t>Break-even</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E88" s="12" t="inlineStr">
+        <is>
+          <t>Cash &amp; Cash Flow</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E89" s="12" t="inlineStr">
+        <is>
+          <t>Ethical &amp; Environmental Considerations</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E90" s="12" t="inlineStr">
+        <is>
+          <t>The Economic Climate &amp; Globalisation</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Business Studies</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Operations, Finance &amp; Influences on Business</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E91" s="12" t="inlineStr">
+        <is>
+          <t>The Interdependent Nature of Business</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H61"/>
+  <autoFilter ref="A1:H91"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/gcse-subject-tracker.xlsx
+++ b/data/gcse-subject-tracker.xlsx
@@ -60,7 +60,7 @@
       <color rgb="00AAAAAA"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +127,12 @@
         <bgColor rgb="00F5F1EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0000FF00"/>
+        <bgColor rgb="0000FF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +160,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -169,6 +175,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -749,8 +758,8 @@
           <t>24 sections</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="n"/>
       <c r="R2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -779,13 +788,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -797,8 +806,8 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr"/>
       <c r="O3" s="2" t="inlineStr"/>
-      <c r="P3" s="2" t="inlineStr"/>
-      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
       <c r="R3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
@@ -827,13 +836,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -845,8 +854,8 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr"/>
       <c r="O4" s="2" t="inlineStr"/>
-      <c r="P4" s="2" t="inlineStr"/>
-      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
       <c r="R4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
@@ -875,13 +884,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -893,8 +902,8 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr"/>
       <c r="O5" s="2" t="inlineStr"/>
-      <c r="P5" s="2" t="inlineStr"/>
-      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="n"/>
+      <c r="Q5" s="2" t="n"/>
       <c r="R5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
@@ -923,13 +932,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1049,13 +1058,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1097,13 +1106,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1145,13 +1154,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1193,13 +1202,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1397,13 +1406,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1445,13 +1454,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -1566,7 +1575,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -1644,7 +1653,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -1722,7 +1731,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -1800,7 +1809,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -1878,7 +1887,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -1956,7 +1965,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -1969,7 +1978,7 @@
       <c r="G22" s="2" t="n">
         <v>197</v>
       </c>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2034,7 +2043,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -2047,7 +2056,7 @@
       <c r="G23" s="2" t="n">
         <v>215</v>
       </c>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2062,7 +2071,7 @@
           <t>215/215</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>108/215</t>
         </is>
@@ -2112,7 +2121,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -2125,7 +2134,7 @@
       <c r="G24" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2190,7 +2199,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -2203,7 +2212,7 @@
       <c r="G25" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2268,7 +2277,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E26" s="8" t="inlineStr">
+      <c r="E26" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -2281,7 +2290,7 @@
       <c r="G26" s="2" t="n">
         <v>182</v>
       </c>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2346,7 +2355,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -2424,7 +2433,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E28" s="7" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -2502,7 +2511,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -2580,7 +2589,7 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
@@ -2658,18 +2667,18 @@
           <t>Core</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -2789,13 +2798,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -2837,13 +2846,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -2885,13 +2894,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -2933,13 +2942,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -2971,23 +2980,23 @@
           <t>J198</t>
         </is>
       </c>
-      <c r="D37" s="11" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="E37" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3023,23 +3032,23 @@
           <t>C650QS</t>
         </is>
       </c>
-      <c r="D38" s="11" t="inlineStr">
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3075,23 +3084,23 @@
           <t>3650QS</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="E39" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3127,23 +3136,23 @@
           <t>8201</t>
         </is>
       </c>
-      <c r="D40" s="11" t="inlineStr">
+      <c r="D40" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E40" s="8" t="inlineStr">
+      <c r="E40" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="9" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3179,23 +3188,23 @@
           <t>1AD0</t>
         </is>
       </c>
-      <c r="D41" s="11" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
+      <c r="E41" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="9" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3231,23 +3240,23 @@
           <t>8202</t>
         </is>
       </c>
-      <c r="D42" s="11" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
+      <c r="E42" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3283,23 +3292,23 @@
           <t>8203</t>
         </is>
       </c>
-      <c r="D43" s="11" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
+      <c r="E43" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3335,23 +3344,23 @@
           <t>8206</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E44" s="8" t="inlineStr">
+      <c r="E44" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3387,23 +3396,23 @@
           <t>8204</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E45" s="8" t="inlineStr">
+      <c r="E45" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="9" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3439,23 +3448,23 @@
           <t>8205</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D46" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
+      <c r="E46" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="9" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3491,23 +3500,23 @@
           <t>8132</t>
         </is>
       </c>
-      <c r="D47" s="11" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E47" s="8" t="inlineStr">
+      <c r="E47" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="9" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3543,23 +3552,23 @@
           <t>1BS0</t>
         </is>
       </c>
-      <c r="D48" s="11" t="inlineStr">
+      <c r="D48" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E48" s="8" t="inlineStr">
+      <c r="E48" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="9" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3595,23 +3604,23 @@
           <t>C510QS</t>
         </is>
       </c>
-      <c r="D49" s="11" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E49" s="8" t="inlineStr">
+      <c r="E49" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3647,23 +3656,23 @@
           <t>J204</t>
         </is>
       </c>
-      <c r="D50" s="11" t="inlineStr">
+      <c r="D50" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
+      <c r="E50" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3699,23 +3708,23 @@
           <t>3510QS</t>
         </is>
       </c>
-      <c r="D51" s="11" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
+      <c r="E51" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="9" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3751,23 +3760,23 @@
           <t>J809</t>
         </is>
       </c>
-      <c r="D52" s="11" t="inlineStr">
+      <c r="D52" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
+      <c r="E52" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="9" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3803,23 +3812,23 @@
           <t>J834</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E53" s="8" t="inlineStr">
+      <c r="E53" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="9" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3855,23 +3864,23 @@
           <t>J822</t>
         </is>
       </c>
-      <c r="D54" s="11" t="inlineStr">
+      <c r="D54" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
+      <c r="E54" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3907,23 +3916,23 @@
           <t>J823</t>
         </is>
       </c>
-      <c r="D55" s="11" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E55" s="8" t="inlineStr">
+      <c r="E55" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="9" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3959,23 +3968,23 @@
           <t>J824</t>
         </is>
       </c>
-      <c r="D56" s="11" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E56" s="8" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="9" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4011,23 +4020,23 @@
           <t>J837</t>
         </is>
       </c>
-      <c r="D57" s="11" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E57" s="8" t="inlineStr">
+      <c r="E57" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="9" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4063,23 +4072,23 @@
           <t>J835</t>
         </is>
       </c>
-      <c r="D58" s="11" t="inlineStr">
+      <c r="D58" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E58" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="9" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4115,23 +4124,23 @@
           <t>J828</t>
         </is>
       </c>
-      <c r="D59" s="11" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E59" s="8" t="inlineStr">
+      <c r="E59" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="9" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4167,23 +4176,23 @@
           <t>J829</t>
         </is>
       </c>
-      <c r="D60" s="11" t="inlineStr">
+      <c r="D60" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
+      <c r="E60" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="9" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4219,23 +4228,23 @@
           <t>8100</t>
         </is>
       </c>
-      <c r="D61" s="11" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
+      <c r="E61" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="9" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4271,23 +4280,23 @@
           <t>1CS0</t>
         </is>
       </c>
-      <c r="D62" s="11" t="inlineStr">
+      <c r="D62" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E62" s="8" t="inlineStr">
+      <c r="E62" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4323,23 +4332,23 @@
           <t>J270</t>
         </is>
       </c>
-      <c r="D63" s="11" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
+      <c r="E63" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="9" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4375,7 +4384,7 @@
           <t>8525</t>
         </is>
       </c>
-      <c r="D64" s="11" t="inlineStr">
+      <c r="D64" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -4385,13 +4394,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr">
+      <c r="H64" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -4427,7 +4436,7 @@
           <t>1CP1</t>
         </is>
       </c>
-      <c r="D65" s="11" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -4437,13 +4446,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F65" s="6" t="inlineStr">
+      <c r="F65" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr">
+      <c r="H65" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -4479,7 +4488,7 @@
           <t>C500QS</t>
         </is>
       </c>
-      <c r="D66" s="11" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -4489,13 +4498,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F66" s="6" t="inlineStr">
+      <c r="F66" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="6" t="inlineStr">
+      <c r="H66" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -4531,7 +4540,7 @@
           <t>J277</t>
         </is>
       </c>
-      <c r="D67" s="11" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -4549,7 +4558,7 @@
       <c r="G67" s="2" t="n">
         <v>23</v>
       </c>
-      <c r="H67" s="6" t="inlineStr">
+      <c r="H67" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -4609,7 +4618,7 @@
           <t>3500QS</t>
         </is>
       </c>
-      <c r="D68" s="11" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -4619,13 +4628,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="6" t="inlineStr">
+      <c r="H68" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -4661,23 +4670,23 @@
           <t>8236</t>
         </is>
       </c>
-      <c r="D69" s="11" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E69" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="9" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4713,12 +4722,12 @@
           <t>8552</t>
         </is>
       </c>
-      <c r="D70" s="11" t="inlineStr">
+      <c r="D70" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
+      <c r="E70" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -4731,7 +4740,7 @@
       <c r="G70" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="H70" s="9" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4791,23 +4800,23 @@
           <t>1DT0</t>
         </is>
       </c>
-      <c r="D71" s="11" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E71" s="8" t="inlineStr">
+      <c r="E71" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="9" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4843,23 +4852,23 @@
           <t>C600QS</t>
         </is>
       </c>
-      <c r="D72" s="11" t="inlineStr">
+      <c r="D72" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="E72" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="9" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4895,23 +4904,23 @@
           <t>J310</t>
         </is>
       </c>
-      <c r="D73" s="11" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E73" s="8" t="inlineStr">
+      <c r="E73" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F73" s="6" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="9" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4947,23 +4956,23 @@
           <t>3600QS</t>
         </is>
       </c>
-      <c r="D74" s="11" t="inlineStr">
+      <c r="D74" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F74" s="6" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="9" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4999,23 +5008,23 @@
           <t>8261</t>
         </is>
       </c>
-      <c r="D75" s="11" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E75" s="8" t="inlineStr">
+      <c r="E75" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="9" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5051,23 +5060,23 @@
           <t>1DR0</t>
         </is>
       </c>
-      <c r="D76" s="11" t="inlineStr">
+      <c r="D76" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E76" s="8" t="inlineStr">
+      <c r="E76" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F76" s="6" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="9" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5103,23 +5112,23 @@
           <t>C690QS</t>
         </is>
       </c>
-      <c r="D77" s="11" t="inlineStr">
+      <c r="D77" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E77" s="8" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F77" s="6" t="inlineStr">
+      <c r="F77" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="9" t="inlineStr">
+      <c r="H77" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5155,23 +5164,23 @@
           <t>J316</t>
         </is>
       </c>
-      <c r="D78" s="11" t="inlineStr">
+      <c r="D78" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E78" s="8" t="inlineStr">
+      <c r="E78" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="9" t="inlineStr">
+      <c r="H78" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5207,23 +5216,23 @@
           <t>3690QS</t>
         </is>
       </c>
-      <c r="D79" s="11" t="inlineStr">
+      <c r="D79" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E79" s="8" t="inlineStr">
+      <c r="E79" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="9" t="inlineStr">
+      <c r="H79" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5259,23 +5268,23 @@
           <t>8136</t>
         </is>
       </c>
-      <c r="D80" s="11" t="inlineStr">
+      <c r="D80" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E80" s="8" t="inlineStr">
+      <c r="E80" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="9" t="inlineStr">
+      <c r="H80" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5311,23 +5320,23 @@
           <t>J205</t>
         </is>
       </c>
-      <c r="D81" s="11" t="inlineStr">
+      <c r="D81" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E81" s="8" t="inlineStr">
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="9" t="inlineStr">
+      <c r="H81" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5363,23 +5372,23 @@
           <t>8852</t>
         </is>
       </c>
-      <c r="D82" s="11" t="inlineStr">
+      <c r="D82" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E82" s="8" t="inlineStr">
+      <c r="E82" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="9" t="inlineStr">
+      <c r="H82" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5415,23 +5424,23 @@
           <t>C670QS</t>
         </is>
       </c>
-      <c r="D83" s="11" t="inlineStr">
+      <c r="D83" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E83" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="9" t="inlineStr">
+      <c r="H83" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5467,23 +5476,23 @@
           <t>3670QS</t>
         </is>
       </c>
-      <c r="D84" s="11" t="inlineStr">
+      <c r="D84" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E84" s="8" t="inlineStr">
+      <c r="E84" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="9" t="inlineStr">
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5519,23 +5528,23 @@
           <t>8585</t>
         </is>
       </c>
-      <c r="D85" s="11" t="inlineStr">
+      <c r="D85" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E85" s="8" t="inlineStr">
+      <c r="E85" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F85" s="6" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="9" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5571,23 +5580,23 @@
           <t>C560QS</t>
         </is>
       </c>
-      <c r="D86" s="11" t="inlineStr">
+      <c r="D86" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E86" s="8" t="inlineStr">
+      <c r="E86" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="9" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5623,23 +5632,23 @@
           <t>J309</t>
         </is>
       </c>
-      <c r="D87" s="11" t="inlineStr">
+      <c r="D87" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E87" s="8" t="inlineStr">
+      <c r="E87" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F87" s="6" t="inlineStr">
+      <c r="F87" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="9" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5675,23 +5684,23 @@
           <t>8652</t>
         </is>
       </c>
-      <c r="D88" s="11" t="inlineStr">
+      <c r="D88" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E88" s="7" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
+      <c r="H88" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -5723,23 +5732,23 @@
           <t>C800QS</t>
         </is>
       </c>
-      <c r="D89" s="11" t="inlineStr">
+      <c r="D89" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E89" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F89" s="6" t="inlineStr">
+      <c r="F89" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="6" t="inlineStr">
+      <c r="H89" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -5771,23 +5780,23 @@
           <t>3800QS</t>
         </is>
       </c>
-      <c r="D90" s="11" t="inlineStr">
+      <c r="D90" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E90" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="6" t="inlineStr">
+      <c r="H90" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -5819,23 +5828,23 @@
           <t>1FR1</t>
         </is>
       </c>
-      <c r="D91" s="11" t="inlineStr">
+      <c r="D91" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E91" s="7" t="inlineStr">
+      <c r="E91" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -5867,23 +5876,23 @@
           <t>8658</t>
         </is>
       </c>
-      <c r="D92" s="11" t="inlineStr">
+      <c r="D92" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E92" s="7" t="inlineStr">
+      <c r="E92" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F92" s="6" t="inlineStr">
+      <c r="F92" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="6" t="inlineStr">
+      <c r="H92" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -5915,7 +5924,7 @@
           <t>8035</t>
         </is>
       </c>
-      <c r="D93" s="11" t="inlineStr">
+      <c r="D93" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -5925,13 +5934,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F93" s="6" t="inlineStr">
+      <c r="F93" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="6" t="inlineStr">
+      <c r="H93" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -5967,7 +5976,7 @@
           <t>3111QS</t>
         </is>
       </c>
-      <c r="D94" s="11" t="inlineStr">
+      <c r="D94" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -5977,13 +5986,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="6" t="inlineStr">
+      <c r="H94" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6019,7 +6028,7 @@
           <t>1GA0</t>
         </is>
       </c>
-      <c r="D95" s="11" t="inlineStr">
+      <c r="D95" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -6029,13 +6038,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="6" t="inlineStr">
+      <c r="H95" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6071,7 +6080,7 @@
           <t>C111QS</t>
         </is>
       </c>
-      <c r="D96" s="11" t="inlineStr">
+      <c r="D96" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -6081,13 +6090,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="6" t="inlineStr">
+      <c r="H96" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6123,7 +6132,7 @@
           <t>J383</t>
         </is>
       </c>
-      <c r="D97" s="11" t="inlineStr">
+      <c r="D97" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -6133,13 +6142,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="6" t="inlineStr">
+      <c r="H97" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6175,7 +6184,7 @@
           <t>1GB0</t>
         </is>
       </c>
-      <c r="D98" s="11" t="inlineStr">
+      <c r="D98" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -6185,13 +6194,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="6" t="inlineStr">
+      <c r="H98" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6227,7 +6236,7 @@
           <t>C112QS</t>
         </is>
       </c>
-      <c r="D99" s="11" t="inlineStr">
+      <c r="D99" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -6237,13 +6246,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="6" t="inlineStr">
+      <c r="H99" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6279,7 +6288,7 @@
           <t>J384</t>
         </is>
       </c>
-      <c r="D100" s="11" t="inlineStr">
+      <c r="D100" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -6289,13 +6298,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="6" t="inlineStr">
+      <c r="H100" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6331,23 +6340,23 @@
           <t>8662</t>
         </is>
       </c>
-      <c r="D101" s="11" t="inlineStr">
+      <c r="D101" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E101" s="7" t="inlineStr">
+      <c r="E101" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
+      <c r="F101" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="6" t="inlineStr">
+      <c r="H101" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6379,23 +6388,23 @@
           <t>3810QS</t>
         </is>
       </c>
-      <c r="D102" s="11" t="inlineStr">
+      <c r="D102" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E102" s="7" t="inlineStr">
+      <c r="E102" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F102" s="6" t="inlineStr">
+      <c r="F102" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="6" t="inlineStr">
+      <c r="H102" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6427,23 +6436,23 @@
           <t>1GN1</t>
         </is>
       </c>
-      <c r="D103" s="11" t="inlineStr">
+      <c r="D103" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="E103" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F103" s="6" t="inlineStr">
+      <c r="F103" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="6" t="inlineStr">
+      <c r="H103" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6475,23 +6484,23 @@
           <t>8668</t>
         </is>
       </c>
-      <c r="D104" s="11" t="inlineStr">
+      <c r="D104" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E104" s="7" t="inlineStr">
+      <c r="E104" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="6" t="inlineStr">
+      <c r="H104" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6523,23 +6532,23 @@
           <t>8145</t>
         </is>
       </c>
-      <c r="D105" s="11" t="inlineStr">
+      <c r="D105" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E105" s="8" t="inlineStr">
+      <c r="E105" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="9" t="inlineStr">
+      <c r="H105" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6575,12 +6584,12 @@
           <t>1HI0</t>
         </is>
       </c>
-      <c r="D106" s="11" t="inlineStr">
+      <c r="D106" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E106" s="8" t="inlineStr">
+      <c r="E106" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -6593,7 +6602,7 @@
       <c r="G106" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="H106" s="9" t="inlineStr">
+      <c r="H106" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6653,23 +6662,23 @@
           <t>C100QS</t>
         </is>
       </c>
-      <c r="D107" s="11" t="inlineStr">
+      <c r="D107" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E107" s="8" t="inlineStr">
+      <c r="E107" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F107" s="6" t="inlineStr">
+      <c r="F107" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="9" t="inlineStr">
+      <c r="H107" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6705,23 +6714,23 @@
           <t>3100QS</t>
         </is>
       </c>
-      <c r="D108" s="11" t="inlineStr">
+      <c r="D108" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E108" s="8" t="inlineStr">
+      <c r="E108" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="9" t="inlineStr">
+      <c r="H108" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6757,23 +6766,23 @@
           <t>J410</t>
         </is>
       </c>
-      <c r="D109" s="11" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E109" s="8" t="inlineStr">
+      <c r="E109" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="9" t="inlineStr">
+      <c r="H109" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6809,23 +6818,23 @@
           <t>J411</t>
         </is>
       </c>
-      <c r="D110" s="11" t="inlineStr">
+      <c r="D110" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E110" s="8" t="inlineStr">
+      <c r="E110" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F110" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="9" t="inlineStr">
+      <c r="H110" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6861,23 +6870,23 @@
           <t>8633</t>
         </is>
       </c>
-      <c r="D111" s="11" t="inlineStr">
+      <c r="D111" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E111" s="7" t="inlineStr">
+      <c r="E111" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="6" t="inlineStr">
+      <c r="H111" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6909,23 +6918,23 @@
           <t>1IN0</t>
         </is>
       </c>
-      <c r="D112" s="11" t="inlineStr">
+      <c r="D112" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E112" s="7" t="inlineStr">
+      <c r="E112" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F112" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="6" t="inlineStr">
+      <c r="H112" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -6957,23 +6966,23 @@
           <t>C580QS</t>
         </is>
       </c>
-      <c r="D113" s="11" t="inlineStr">
+      <c r="D113" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E113" s="7" t="inlineStr">
+      <c r="E113" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="6" t="inlineStr">
+      <c r="H113" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7009,23 +7018,23 @@
           <t>J282</t>
         </is>
       </c>
-      <c r="D114" s="11" t="inlineStr">
+      <c r="D114" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E114" s="7" t="inlineStr">
+      <c r="E114" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="6" t="inlineStr">
+      <c r="H114" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7061,23 +7070,23 @@
           <t>3580QS</t>
         </is>
       </c>
-      <c r="D115" s="11" t="inlineStr">
+      <c r="D115" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E115" s="7" t="inlineStr">
+      <c r="E115" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F115" s="6" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="6" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7113,23 +7122,23 @@
           <t>5239QA</t>
         </is>
       </c>
-      <c r="D116" s="11" t="inlineStr">
+      <c r="D116" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E116" s="8" t="inlineStr">
+      <c r="E116" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F116" s="6" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="9" t="inlineStr">
+      <c r="H116" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7165,23 +7174,23 @@
           <t>5879QA</t>
         </is>
       </c>
-      <c r="D117" s="11" t="inlineStr">
+      <c r="D117" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E117" s="7" t="inlineStr">
+      <c r="E117" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F117" s="6" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="6" t="inlineStr">
+      <c r="H117" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7213,23 +7222,23 @@
           <t>5879QA</t>
         </is>
       </c>
-      <c r="D118" s="11" t="inlineStr">
+      <c r="D118" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E118" s="7" t="inlineStr">
+      <c r="E118" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F118" s="6" t="inlineStr">
+      <c r="F118" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="6" t="inlineStr">
+      <c r="H118" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7261,23 +7270,23 @@
           <t>5889QA</t>
         </is>
       </c>
-      <c r="D119" s="11" t="inlineStr">
+      <c r="D119" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E119" s="7" t="inlineStr">
+      <c r="E119" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F119" s="6" t="inlineStr">
+      <c r="F119" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="6" t="inlineStr">
+      <c r="H119" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7309,23 +7318,23 @@
           <t>5899QA</t>
         </is>
       </c>
-      <c r="D120" s="11" t="inlineStr">
+      <c r="D120" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E120" s="7" t="inlineStr">
+      <c r="E120" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F120" s="6" t="inlineStr">
+      <c r="F120" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="6" t="inlineStr">
+      <c r="H120" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7357,23 +7366,23 @@
           <t>5899QA</t>
         </is>
       </c>
-      <c r="D121" s="11" t="inlineStr">
+      <c r="D121" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E121" s="7" t="inlineStr">
+      <c r="E121" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F121" s="6" t="inlineStr">
+      <c r="F121" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="6" t="inlineStr">
+      <c r="H121" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -7405,23 +7414,23 @@
           <t>5249QA</t>
         </is>
       </c>
-      <c r="D122" s="11" t="inlineStr">
+      <c r="D122" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E122" s="8" t="inlineStr">
+      <c r="E122" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="9" t="inlineStr">
+      <c r="H122" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7457,12 +7466,12 @@
           <t>5409QA</t>
         </is>
       </c>
-      <c r="D123" s="11" t="inlineStr">
+      <c r="D123" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E123" s="8" t="inlineStr">
+      <c r="E123" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -7475,7 +7484,7 @@
       <c r="G123" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H123" s="9" t="inlineStr">
+      <c r="H123" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7535,12 +7544,12 @@
           <t>5409QA</t>
         </is>
       </c>
-      <c r="D124" s="11" t="inlineStr">
+      <c r="D124" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E124" s="8" t="inlineStr">
+      <c r="E124" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -7553,7 +7562,7 @@
       <c r="G124" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="H124" s="9" t="inlineStr">
+      <c r="H124" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7613,23 +7622,23 @@
           <t>5299QA</t>
         </is>
       </c>
-      <c r="D125" s="11" t="inlineStr">
+      <c r="D125" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E125" s="8" t="inlineStr">
+      <c r="E125" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="9" t="inlineStr">
+      <c r="H125" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7665,23 +7674,23 @@
           <t>8572</t>
         </is>
       </c>
-      <c r="D126" s="11" t="inlineStr">
+      <c r="D126" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E126" s="8" t="inlineStr">
+      <c r="E126" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="9" t="inlineStr">
+      <c r="H126" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7717,23 +7726,23 @@
           <t>C680QS</t>
         </is>
       </c>
-      <c r="D127" s="11" t="inlineStr">
+      <c r="D127" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E127" s="8" t="inlineStr">
+      <c r="E127" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="9" t="inlineStr">
+      <c r="H127" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7769,23 +7778,23 @@
           <t>J200</t>
         </is>
       </c>
-      <c r="D128" s="11" t="inlineStr">
+      <c r="D128" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E128" s="8" t="inlineStr">
+      <c r="E128" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F128" s="6" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="9" t="inlineStr">
+      <c r="H128" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7821,23 +7830,23 @@
           <t>3680QS</t>
         </is>
       </c>
-      <c r="D129" s="11" t="inlineStr">
+      <c r="D129" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E129" s="8" t="inlineStr">
+      <c r="E129" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F129" s="6" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="9" t="inlineStr">
+      <c r="H129" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7873,23 +7882,23 @@
           <t>8271</t>
         </is>
       </c>
-      <c r="D130" s="11" t="inlineStr">
+      <c r="D130" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E130" s="8" t="inlineStr">
+      <c r="E130" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F130" s="6" t="inlineStr">
+      <c r="F130" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="9" t="inlineStr">
+      <c r="H130" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7925,23 +7934,23 @@
           <t>1MU0</t>
         </is>
       </c>
-      <c r="D131" s="11" t="inlineStr">
+      <c r="D131" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E131" s="8" t="inlineStr">
+      <c r="E131" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F131" s="6" t="inlineStr">
+      <c r="F131" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="9" t="inlineStr">
+      <c r="H131" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7977,23 +7986,23 @@
           <t>C660QS</t>
         </is>
       </c>
-      <c r="D132" s="11" t="inlineStr">
+      <c r="D132" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E132" s="8" t="inlineStr">
+      <c r="E132" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F132" s="6" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="9" t="inlineStr">
+      <c r="H132" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8029,23 +8038,23 @@
           <t>J536</t>
         </is>
       </c>
-      <c r="D133" s="11" t="inlineStr">
+      <c r="D133" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E133" s="8" t="inlineStr">
+      <c r="E133" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F133" s="6" t="inlineStr">
+      <c r="F133" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="9" t="inlineStr">
+      <c r="H133" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8081,23 +8090,23 @@
           <t>3660QS</t>
         </is>
       </c>
-      <c r="D134" s="11" t="inlineStr">
+      <c r="D134" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E134" s="8" t="inlineStr">
+      <c r="E134" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F134" s="6" t="inlineStr">
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="9" t="inlineStr">
+      <c r="H134" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8133,7 +8142,7 @@
           <t>8582</t>
         </is>
       </c>
-      <c r="D135" s="11" t="inlineStr">
+      <c r="D135" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8143,13 +8152,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F135" s="6" t="inlineStr">
+      <c r="F135" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="6" t="inlineStr">
+      <c r="H135" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8185,7 +8194,7 @@
           <t>1PE0</t>
         </is>
       </c>
-      <c r="D136" s="11" t="inlineStr">
+      <c r="D136" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8195,13 +8204,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F136" s="6" t="inlineStr">
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="6" t="inlineStr">
+      <c r="H136" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8237,7 +8246,7 @@
           <t>C550QS</t>
         </is>
       </c>
-      <c r="D137" s="11" t="inlineStr">
+      <c r="D137" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8247,13 +8256,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F137" s="6" t="inlineStr">
+      <c r="F137" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="6" t="inlineStr">
+      <c r="H137" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8289,7 +8298,7 @@
           <t>J587</t>
         </is>
       </c>
-      <c r="D138" s="11" t="inlineStr">
+      <c r="D138" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8299,13 +8308,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F138" s="6" t="inlineStr">
+      <c r="F138" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="6" t="inlineStr">
+      <c r="H138" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8341,7 +8350,7 @@
           <t>3550QS</t>
         </is>
       </c>
-      <c r="D139" s="11" t="inlineStr">
+      <c r="D139" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8351,13 +8360,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F139" s="6" t="inlineStr">
+      <c r="F139" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="6" t="inlineStr">
+      <c r="H139" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8393,7 +8402,7 @@
           <t>8182</t>
         </is>
       </c>
-      <c r="D140" s="11" t="inlineStr">
+      <c r="D140" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8403,13 +8412,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F140" s="6" t="inlineStr">
+      <c r="F140" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="6" t="inlineStr">
+      <c r="H140" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8445,7 +8454,7 @@
           <t>1PS0</t>
         </is>
       </c>
-      <c r="D141" s="11" t="inlineStr">
+      <c r="D141" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8455,13 +8464,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F141" s="6" t="inlineStr">
+      <c r="F141" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="6" t="inlineStr">
+      <c r="H141" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8497,7 +8506,7 @@
           <t>J203</t>
         </is>
       </c>
-      <c r="D142" s="11" t="inlineStr">
+      <c r="D142" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -8507,13 +8516,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F142" s="6" t="inlineStr">
+      <c r="F142" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="6" t="inlineStr">
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -8549,23 +8558,23 @@
           <t>C120QS</t>
         </is>
       </c>
-      <c r="D143" s="11" t="inlineStr">
+      <c r="D143" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E143" s="8" t="inlineStr">
+      <c r="E143" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F143" s="6" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="9" t="inlineStr">
+      <c r="H143" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8601,23 +8610,23 @@
           <t>3120QS</t>
         </is>
       </c>
-      <c r="D144" s="11" t="inlineStr">
+      <c r="D144" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E144" s="8" t="inlineStr">
+      <c r="E144" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F144" s="6" t="inlineStr">
+      <c r="F144" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="9" t="inlineStr">
+      <c r="H144" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8653,23 +8662,23 @@
           <t>J625</t>
         </is>
       </c>
-      <c r="D145" s="11" t="inlineStr">
+      <c r="D145" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E145" s="8" t="inlineStr">
+      <c r="E145" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F145" s="6" t="inlineStr">
+      <c r="F145" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="9" t="inlineStr">
+      <c r="H145" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8705,23 +8714,23 @@
           <t>8061</t>
         </is>
       </c>
-      <c r="D146" s="11" t="inlineStr">
+      <c r="D146" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E146" s="8" t="inlineStr">
+      <c r="E146" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F146" s="6" t="inlineStr">
+      <c r="F146" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="9" t="inlineStr">
+      <c r="H146" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8757,23 +8766,23 @@
           <t>J125</t>
         </is>
       </c>
-      <c r="D147" s="11" t="inlineStr">
+      <c r="D147" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E147" s="8" t="inlineStr">
+      <c r="E147" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F147" s="6" t="inlineStr">
+      <c r="F147" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="9" t="inlineStr">
+      <c r="H147" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8809,12 +8818,12 @@
           <t>8062</t>
         </is>
       </c>
-      <c r="D148" s="11" t="inlineStr">
+      <c r="D148" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E148" s="8" t="inlineStr">
+      <c r="E148" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
@@ -8827,7 +8836,7 @@
       <c r="G148" s="2" t="n">
         <v>28</v>
       </c>
-      <c r="H148" s="9" t="inlineStr">
+      <c r="H148" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8887,23 +8896,23 @@
           <t>1RA0</t>
         </is>
       </c>
-      <c r="D149" s="11" t="inlineStr">
+      <c r="D149" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E149" s="8" t="inlineStr">
+      <c r="E149" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F149" s="6" t="inlineStr">
+      <c r="F149" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="9" t="inlineStr">
+      <c r="H149" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8939,23 +8948,23 @@
           <t>8063</t>
         </is>
       </c>
-      <c r="D150" s="11" t="inlineStr">
+      <c r="D150" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E150" s="8" t="inlineStr">
+      <c r="E150" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F150" s="6" t="inlineStr">
+      <c r="F150" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="9" t="inlineStr">
+      <c r="H150" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8991,23 +9000,23 @@
           <t>8192</t>
         </is>
       </c>
-      <c r="D151" s="11" t="inlineStr">
+      <c r="D151" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E151" s="8" t="inlineStr">
+      <c r="E151" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F151" s="6" t="inlineStr">
+      <c r="F151" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="9" t="inlineStr">
+      <c r="H151" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9043,23 +9052,23 @@
           <t>C200QS</t>
         </is>
       </c>
-      <c r="D152" s="11" t="inlineStr">
+      <c r="D152" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E152" s="8" t="inlineStr">
+      <c r="E152" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F152" s="6" t="inlineStr">
+      <c r="F152" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="9" t="inlineStr">
+      <c r="H152" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9095,23 +9104,23 @@
           <t>3200QS</t>
         </is>
       </c>
-      <c r="D153" s="11" t="inlineStr">
+      <c r="D153" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E153" s="8" t="inlineStr">
+      <c r="E153" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F153" s="6" t="inlineStr">
+      <c r="F153" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="9" t="inlineStr">
+      <c r="H153" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9147,23 +9156,23 @@
           <t>8692</t>
         </is>
       </c>
-      <c r="D154" s="11" t="inlineStr">
+      <c r="D154" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
+      <c r="E154" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
+      <c r="F154" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
+      <c r="H154" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9195,23 +9204,23 @@
           <t>C820QS</t>
         </is>
       </c>
-      <c r="D155" s="11" t="inlineStr">
+      <c r="D155" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E155" s="7" t="inlineStr">
+      <c r="E155" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F155" s="6" t="inlineStr">
+      <c r="F155" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="6" t="inlineStr">
+      <c r="H155" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9243,23 +9252,23 @@
           <t>3820QS</t>
         </is>
       </c>
-      <c r="D156" s="11" t="inlineStr">
+      <c r="D156" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E156" s="7" t="inlineStr">
+      <c r="E156" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F156" s="6" t="inlineStr">
+      <c r="F156" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="6" t="inlineStr">
+      <c r="H156" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9291,23 +9300,23 @@
           <t>1SP1</t>
         </is>
       </c>
-      <c r="D157" s="11" t="inlineStr">
+      <c r="D157" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E157" s="7" t="inlineStr">
+      <c r="E157" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F157" s="6" t="inlineStr">
+      <c r="F157" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="6" t="inlineStr">
+      <c r="H157" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9339,23 +9348,23 @@
           <t>8698</t>
         </is>
       </c>
-      <c r="D158" s="11" t="inlineStr">
+      <c r="D158" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
       </c>
-      <c r="E158" s="7" t="inlineStr">
+      <c r="E158" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F158" s="6" t="inlineStr">
+      <c r="F158" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="6" t="inlineStr">
+      <c r="H158" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9387,7 +9396,7 @@
           <t>8382</t>
         </is>
       </c>
-      <c r="D159" s="11" t="inlineStr">
+      <c r="D159" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -9397,13 +9406,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F159" s="6" t="inlineStr">
+      <c r="F159" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="6" t="inlineStr">
+      <c r="H159" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9435,7 +9444,7 @@
           <t>1ST0</t>
         </is>
       </c>
-      <c r="D160" s="11" t="inlineStr">
+      <c r="D160" s="12" t="inlineStr">
         <is>
           <t>High demand</t>
         </is>
@@ -9445,13 +9454,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F160" s="6" t="inlineStr">
+      <c r="F160" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="6" t="inlineStr">
+      <c r="H160" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9476,18 +9485,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E161" s="8" t="inlineStr">
+      <c r="E161" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F161" s="6" t="inlineStr">
+      <c r="F161" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="9" t="inlineStr">
+      <c r="H161" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9528,18 +9537,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E162" s="7" t="inlineStr">
+      <c r="E162" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F162" s="6" t="inlineStr">
+      <c r="F162" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="6" t="inlineStr">
+      <c r="H162" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9580,18 +9589,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E163" s="8" t="inlineStr">
+      <c r="E163" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F163" s="6" t="inlineStr">
+      <c r="F163" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="9" t="inlineStr">
+      <c r="H163" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9632,18 +9641,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E164" s="7" t="inlineStr">
+      <c r="E164" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F164" s="6" t="inlineStr">
+      <c r="F164" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="6" t="inlineStr">
+      <c r="H164" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9684,18 +9693,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E165" s="7" t="inlineStr">
+      <c r="E165" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F165" s="6" t="inlineStr">
+      <c r="F165" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="6" t="inlineStr">
+      <c r="H165" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9736,18 +9745,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E166" s="8" t="inlineStr">
+      <c r="E166" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F166" s="6" t="inlineStr">
+      <c r="F166" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="9" t="inlineStr">
+      <c r="H166" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9788,18 +9797,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E167" s="7" t="inlineStr">
+      <c r="E167" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F167" s="6" t="inlineStr">
+      <c r="F167" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="6" t="inlineStr">
+      <c r="H167" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9840,18 +9849,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E168" s="7" t="inlineStr">
+      <c r="E168" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F168" s="6" t="inlineStr">
+      <c r="F168" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="6" t="inlineStr">
+      <c r="H168" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -9892,18 +9901,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E169" s="8" t="inlineStr">
+      <c r="E169" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F169" s="6" t="inlineStr">
+      <c r="F169" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="9" t="inlineStr">
+      <c r="H169" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -9944,18 +9953,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E170" s="7" t="inlineStr">
+      <c r="E170" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F170" s="6" t="inlineStr">
+      <c r="F170" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="6" t="inlineStr">
+      <c r="H170" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10001,13 +10010,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F171" s="6" t="inlineStr">
+      <c r="F171" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="6" t="inlineStr">
+      <c r="H171" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10053,13 +10062,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F172" s="6" t="inlineStr">
+      <c r="F172" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="6" t="inlineStr">
+      <c r="H172" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10100,18 +10109,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E173" s="8" t="inlineStr">
+      <c r="E173" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F173" s="6" t="inlineStr">
+      <c r="F173" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="9" t="inlineStr">
+      <c r="H173" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10157,13 +10166,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F174" s="6" t="inlineStr">
+      <c r="F174" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="6" t="inlineStr">
+      <c r="H174" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10209,13 +10218,13 @@
           <t>Mixed</t>
         </is>
       </c>
-      <c r="F175" s="6" t="inlineStr">
+      <c r="F175" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="6" t="inlineStr">
+      <c r="H175" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10256,18 +10265,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E176" s="7" t="inlineStr">
+      <c r="E176" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F176" s="6" t="inlineStr">
+      <c r="F176" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="6" t="inlineStr">
+      <c r="H176" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10308,18 +10317,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E177" s="7" t="inlineStr">
+      <c r="E177" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F177" s="6" t="inlineStr">
+      <c r="F177" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="6" t="inlineStr">
+      <c r="H177" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10360,18 +10369,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E178" s="7" t="inlineStr">
+      <c r="E178" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F178" s="6" t="inlineStr">
+      <c r="F178" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="6" t="inlineStr">
+      <c r="H178" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10412,18 +10421,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E179" s="7" t="inlineStr">
+      <c r="E179" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F179" s="6" t="inlineStr">
+      <c r="F179" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="6" t="inlineStr">
+      <c r="H179" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10464,18 +10473,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E180" s="8" t="inlineStr">
+      <c r="E180" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F180" s="6" t="inlineStr">
+      <c r="F180" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="9" t="inlineStr">
+      <c r="H180" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10516,18 +10525,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E181" s="8" t="inlineStr">
+      <c r="E181" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F181" s="6" t="inlineStr">
+      <c r="F181" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="9" t="inlineStr">
+      <c r="H181" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10568,18 +10577,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E182" s="8" t="inlineStr">
+      <c r="E182" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F182" s="6" t="inlineStr">
+      <c r="F182" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="9" t="inlineStr">
+      <c r="H182" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10620,18 +10629,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E183" s="8" t="inlineStr">
+      <c r="E183" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F183" s="6" t="inlineStr">
+      <c r="F183" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="9" t="inlineStr">
+      <c r="H183" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -10672,18 +10681,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E184" s="7" t="inlineStr">
+      <c r="E184" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F184" s="6" t="inlineStr">
+      <c r="F184" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="6" t="inlineStr">
+      <c r="H184" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10724,18 +10733,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E185" s="7" t="inlineStr">
+      <c r="E185" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F185" s="6" t="inlineStr">
+      <c r="F185" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="6" t="inlineStr">
+      <c r="H185" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10776,18 +10785,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E186" s="7" t="inlineStr">
+      <c r="E186" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F186" s="6" t="inlineStr">
+      <c r="F186" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="6" t="inlineStr">
+      <c r="H186" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10828,18 +10837,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E187" s="7" t="inlineStr">
+      <c r="E187" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F187" s="6" t="inlineStr">
+      <c r="F187" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="6" t="inlineStr">
+      <c r="H187" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10880,18 +10889,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E188" s="7" t="inlineStr">
+      <c r="E188" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F188" s="6" t="inlineStr">
+      <c r="F188" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="6" t="inlineStr">
+      <c r="H188" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10932,18 +10941,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E189" s="7" t="inlineStr">
+      <c r="E189" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F189" s="6" t="inlineStr">
+      <c r="F189" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr"/>
-      <c r="H189" s="6" t="inlineStr">
+      <c r="H189" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -10984,18 +10993,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E190" s="7" t="inlineStr">
+      <c r="E190" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F190" s="6" t="inlineStr">
+      <c r="F190" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr"/>
-      <c r="H190" s="6" t="inlineStr">
+      <c r="H190" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -11036,18 +11045,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E191" s="7" t="inlineStr">
+      <c r="E191" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F191" s="6" t="inlineStr">
+      <c r="F191" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G191" s="2" t="inlineStr"/>
-      <c r="H191" s="6" t="inlineStr">
+      <c r="H191" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -11088,18 +11097,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E192" s="7" t="inlineStr">
+      <c r="E192" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F192" s="6" t="inlineStr">
+      <c r="F192" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G192" s="2" t="inlineStr"/>
-      <c r="H192" s="6" t="inlineStr">
+      <c r="H192" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -11140,18 +11149,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E193" s="8" t="inlineStr">
+      <c r="E193" s="9" t="inlineStr">
         <is>
           <t>Article</t>
         </is>
       </c>
-      <c r="F193" s="6" t="inlineStr">
+      <c r="F193" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G193" s="2" t="inlineStr"/>
-      <c r="H193" s="9" t="inlineStr">
+      <c r="H193" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -11192,18 +11201,18 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="E194" s="7" t="inlineStr">
+      <c r="E194" s="8" t="inlineStr">
         <is>
           <t>Practice</t>
         </is>
       </c>
-      <c r="F194" s="6" t="inlineStr">
+      <c r="F194" s="7" t="inlineStr">
         <is>
           <t>Not built</t>
         </is>
       </c>
       <c r="G194" s="2" t="inlineStr"/>
-      <c r="H194" s="6" t="inlineStr">
+      <c r="H194" s="7" t="inlineStr">
         <is>
           <t>Needs building</t>
         </is>
@@ -11309,7 +11318,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Types of Hospitality &amp; Catering Provision</t>
         </is>
@@ -11341,7 +11350,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Food Service Styles &amp; Residential Services</t>
         </is>
@@ -11373,7 +11382,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Job Roles &amp; the Kitchen Brigade</t>
         </is>
@@ -11405,7 +11414,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Working Conditions &amp; Employment</t>
         </is>
@@ -11437,7 +11446,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Business Success Factors</t>
         </is>
@@ -11469,7 +11478,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Front &amp; Back of House Operations</t>
         </is>
@@ -11501,7 +11510,7 @@
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Customer Requirements &amp; Meeting Specific Needs</t>
         </is>
@@ -11533,7 +11542,7 @@
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Health &amp; Safety Legislation</t>
         </is>
@@ -11565,7 +11574,7 @@
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Food Safety: Bacteria, Allergens &amp; Intolerances</t>
         </is>
@@ -11597,7 +11606,7 @@
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Symptoms, Prevention &amp; the Environmental Health Officer</t>
         </is>
@@ -11696,7 +11705,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Roles &amp; Responsibilities in the Music Business</t>
         </is>
@@ -11728,7 +11737,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>The Development of Music Technology</t>
         </is>
@@ -11760,7 +11769,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Marketing, Promotion &amp; Distribution</t>
         </is>
@@ -11792,7 +11801,7 @@
       <c r="D5" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>DAW Hardware Components</t>
         </is>
@@ -11824,7 +11833,7 @@
       <c r="D6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>DAW Software Functions</t>
         </is>
@@ -11856,7 +11865,7 @@
       <c r="D7" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Creating Audio with a DAW &amp; Health and Safety</t>
         </is>
@@ -11888,7 +11897,7 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Structural Sections, Form &amp; Melody</t>
         </is>
@@ -11920,7 +11929,7 @@
       <c r="D9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Harmony, Rhythm &amp; Instrumentation</t>
         </is>
@@ -11952,7 +11961,7 @@
       <c r="D10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Musical Styles &amp; Technology Through the Decades</t>
         </is>
@@ -11984,7 +11993,7 @@
       <c r="D11" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Sound Creation for Media</t>
         </is>
@@ -12016,7 +12025,7 @@
       <c r="D12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Methods of Sound Creation</t>
         </is>
@@ -12048,7 +12057,7 @@
       <c r="D13" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Arranging &amp; Exporting Sounds</t>
         </is>
@@ -12080,7 +12089,7 @@
       <c r="D14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Recording Studio Equipment &amp; Safety</t>
         </is>
@@ -12112,7 +12121,7 @@
       <c r="D15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Planning &amp; Undertaking Multitrack Recordings</t>
         </is>
@@ -12144,7 +12153,7 @@
       <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Mixing &amp; Stereo Mixdowns</t>
         </is>
@@ -12243,7 +12252,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Purpose of Business &amp; Entrepreneurship</t>
         </is>
@@ -12275,7 +12284,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Business Ownership &amp; Limited Liability</t>
         </is>
@@ -12307,7 +12316,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Business Aims &amp; Objectives</t>
         </is>
@@ -12339,7 +12348,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Stakeholders &amp; Their Influence</t>
         </is>
@@ -12371,7 +12380,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Business Location</t>
         </is>
@@ -12403,7 +12412,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Business Planning &amp; Expansion</t>
         </is>
@@ -12435,7 +12444,7 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Technology &amp; Digital Communication</t>
         </is>
@@ -12467,7 +12476,7 @@
       <c r="D9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Ethics, Environment &amp; Sustainability</t>
         </is>
@@ -12499,7 +12508,7 @@
       <c r="D10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>The Economic Climate</t>
         </is>
@@ -12531,7 +12540,7 @@
       <c r="D11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Globalisation &amp; Exchange Rates</t>
         </is>
@@ -12563,7 +12572,7 @@
       <c r="D12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Legislation &amp; Competition</t>
         </is>
@@ -12595,7 +12604,7 @@
       <c r="D13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Production Processes</t>
         </is>
@@ -12627,7 +12636,7 @@
       <c r="D14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Procurement &amp; Supply Chains</t>
         </is>
@@ -12659,7 +12668,7 @@
       <c r="D15" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Quality</t>
         </is>
@@ -12691,7 +12700,7 @@
       <c r="D16" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Customer Service</t>
         </is>
@@ -12723,7 +12732,7 @@
       <c r="D17" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Organisational Structures</t>
         </is>
@@ -12755,7 +12764,7 @@
       <c r="D18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Recruitment &amp; Selection</t>
         </is>
@@ -12787,7 +12796,7 @@
       <c r="D19" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Motivation</t>
         </is>
@@ -12819,7 +12828,7 @@
       <c r="D20" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Training</t>
         </is>
@@ -12851,7 +12860,7 @@
       <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Identifying Customers &amp; Segmentation</t>
         </is>
@@ -12883,7 +12892,7 @@
       <c r="D22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Market Research</t>
         </is>
@@ -12915,7 +12924,7 @@
       <c r="D23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Product &amp; Pricing</t>
         </is>
@@ -12947,7 +12956,7 @@
       <c r="D24" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Product Life Cycle &amp; Boston Matrix</t>
         </is>
@@ -12979,7 +12988,7 @@
       <c r="D25" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Promotion</t>
         </is>
@@ -13011,7 +13020,7 @@
       <c r="D26" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Place &amp; E-commerce</t>
         </is>
@@ -13043,7 +13052,7 @@
       <c r="D27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Sources of Finance</t>
         </is>
@@ -13075,7 +13084,7 @@
       <c r="D28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Cash Flow</t>
         </is>
@@ -13107,7 +13116,7 @@
       <c r="D29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Costs, Revenue &amp; Profit</t>
         </is>
@@ -13139,7 +13148,7 @@
       <c r="D30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Break-even &amp; Average Rate of Return</t>
         </is>
@@ -13171,7 +13180,7 @@
       <c r="D31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Analysing Financial Performance</t>
         </is>
@@ -13203,7 +13212,7 @@
       <c r="D32" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Why &amp; How New Business Ideas Come About</t>
         </is>
@@ -13235,7 +13244,7 @@
       <c r="D33" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Risk &amp; Reward in Enterprise</t>
         </is>
@@ -13267,7 +13276,7 @@
       <c r="D34" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>The Role of Business Enterprise &amp; Adding Value</t>
         </is>
@@ -13299,7 +13308,7 @@
       <c r="D35" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Customer Needs</t>
         </is>
@@ -13331,7 +13340,7 @@
       <c r="D36" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Market Research</t>
         </is>
@@ -13363,7 +13372,7 @@
       <c r="D37" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Market Segmentation &amp; Market Mapping</t>
         </is>
@@ -13395,7 +13404,7 @@
       <c r="D38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>The Competitive Environment</t>
         </is>
@@ -13427,7 +13436,7 @@
       <c r="D39" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Business Aims &amp; Objectives</t>
         </is>
@@ -13459,7 +13468,7 @@
       <c r="D40" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Revenue, Costs, Profit &amp; Break-even</t>
         </is>
@@ -13491,7 +13500,7 @@
       <c r="D41" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Flow Forecasts</t>
         </is>
@@ -13523,7 +13532,7 @@
       <c r="D42" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Sources of Finance for Start-ups</t>
         </is>
@@ -13555,7 +13564,7 @@
       <c r="D43" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Limited Liability &amp; Ownership for Start-ups</t>
         </is>
@@ -13587,7 +13596,7 @@
       <c r="D44" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Business Location &amp; the Marketing Mix</t>
         </is>
@@ -13619,7 +13628,7 @@
       <c r="D45" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Business Plans</t>
         </is>
@@ -13651,7 +13660,7 @@
       <c r="D46" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Stakeholders, Technology, Legislation &amp; the Economy</t>
         </is>
@@ -13683,7 +13692,7 @@
       <c r="D47" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>Business Growth &amp; Changing Ownership</t>
         </is>
@@ -13715,7 +13724,7 @@
       <c r="D48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Changes in Aims &amp; Objectives</t>
         </is>
@@ -13747,7 +13756,7 @@
       <c r="D49" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Globalisation &amp; International Trade</t>
         </is>
@@ -13779,7 +13788,7 @@
       <c r="D50" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Ethics, Environment &amp; Sustainability</t>
         </is>
@@ -13811,7 +13820,7 @@
       <c r="D51" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>Product &amp; Product Life Cycle</t>
         </is>
@@ -13843,7 +13852,7 @@
       <c r="D52" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>Price &amp; Pricing Strategies</t>
         </is>
@@ -13875,7 +13884,7 @@
       <c r="D53" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Promotion Strategies</t>
         </is>
@@ -13907,7 +13916,7 @@
       <c r="D54" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>Place &amp; the Integrated Marketing Mix</t>
         </is>
@@ -13939,7 +13948,7 @@
       <c r="D55" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>Production Processes</t>
         </is>
@@ -13971,7 +13980,7 @@
       <c r="D56" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>Working with Suppliers &amp; Managing Quality</t>
         </is>
@@ -14003,7 +14012,7 @@
       <c r="D57" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>The Sales Process</t>
         </is>
@@ -14035,7 +14044,7 @@
       <c r="D58" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>Business Calculations: Gross &amp; Net Profit, ARR</t>
         </is>
@@ -14067,7 +14076,7 @@
       <c r="D59" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>Using Data to Understand Business Performance</t>
         </is>
@@ -14099,7 +14108,7 @@
       <c r="D60" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>Organisational Structures &amp; Ways of Working</t>
         </is>
@@ -14131,7 +14140,7 @@
       <c r="D61" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Recruitment, Training &amp; Motivation</t>
         </is>
@@ -14163,7 +14172,7 @@
       <c r="D62" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>Enterprise, Entrepreneurs &amp; Risk and Reward</t>
         </is>
@@ -14195,7 +14204,7 @@
       <c r="D63" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>Business Planning</t>
         </is>
@@ -14227,7 +14236,7 @@
       <c r="D64" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Business Ownership &amp; Limited Liability</t>
         </is>
@@ -14259,7 +14268,7 @@
       <c r="D65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>Business Aims &amp; Objectives</t>
         </is>
@@ -14291,7 +14300,7 @@
       <c r="D66" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>Stakeholders in Business</t>
         </is>
@@ -14323,7 +14332,7 @@
       <c r="D67" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>Business Growth</t>
         </is>
@@ -14355,7 +14364,7 @@
       <c r="D68" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>Role &amp; Purpose of Marketing</t>
         </is>
@@ -14387,7 +14396,7 @@
       <c r="D69" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>Market Research</t>
         </is>
@@ -14419,7 +14428,7 @@
       <c r="D70" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>Market Segmentation</t>
         </is>
@@ -14451,7 +14460,7 @@
       <c r="D71" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>Product &amp; the Product Life Cycle</t>
         </is>
@@ -14483,7 +14492,7 @@
       <c r="D72" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>Pricing Methods</t>
         </is>
@@ -14515,7 +14524,7 @@
       <c r="D73" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>Promotion &amp; Place</t>
         </is>
@@ -14547,7 +14556,7 @@
       <c r="D74" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>The Marketing Mix in Action</t>
         </is>
@@ -14579,7 +14588,7 @@
       <c r="D75" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>Organisational Structures &amp; Ways of Working</t>
         </is>
@@ -14611,7 +14620,7 @@
       <c r="D76" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>Recruitment, Motivation, Training &amp; Employment Law</t>
         </is>
@@ -14643,7 +14652,7 @@
       <c r="D77" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>Production Processes &amp; Technology</t>
         </is>
@@ -14675,7 +14684,7 @@
       <c r="D78" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>Quality of Goods &amp; Services</t>
         </is>
@@ -14707,7 +14716,7 @@
       <c r="D79" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>The Sales Process &amp; Customer Service</t>
         </is>
@@ -14739,7 +14748,7 @@
       <c r="D80" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>Consumer Law</t>
         </is>
@@ -14771,7 +14780,7 @@
       <c r="D81" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>Business Location</t>
         </is>
@@ -14803,7 +14812,7 @@
       <c r="D82" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>Working with Suppliers &amp; Procurement</t>
         </is>
@@ -14835,7 +14844,7 @@
       <c r="D83" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>The Role of the Finance Function</t>
         </is>
@@ -14867,7 +14876,7 @@
       <c r="D84" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>Sources of Finance</t>
         </is>
@@ -14899,7 +14908,7 @@
       <c r="D85" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="13" t="inlineStr">
         <is>
           <t>Revenue, Costs &amp; Profit</t>
         </is>
@@ -14931,7 +14940,7 @@
       <c r="D86" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>Profit Margins &amp; Average Rate of Return</t>
         </is>
@@ -14963,7 +14972,7 @@
       <c r="D87" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E87" s="12" t="inlineStr">
+      <c r="E87" s="13" t="inlineStr">
         <is>
           <t>Break-even</t>
         </is>
@@ -14995,7 +15004,7 @@
       <c r="D88" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E88" s="12" t="inlineStr">
+      <c r="E88" s="13" t="inlineStr">
         <is>
           <t>Cash &amp; Cash Flow</t>
         </is>
@@ -15027,7 +15036,7 @@
       <c r="D89" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>Ethical &amp; Environmental Considerations</t>
         </is>
@@ -15059,7 +15068,7 @@
       <c r="D90" s="2" t="n">
         <v>14</v>
       </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="E90" s="13" t="inlineStr">
         <is>
           <t>The Economic Climate &amp; Globalisation</t>
         </is>
@@ -15091,7 +15100,7 @@
       <c r="D91" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="E91" s="12" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>The Interdependent Nature of Business</t>
         </is>
@@ -15196,7 +15205,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>A Christmas Carol</t>
         </is>
@@ -15236,7 +15245,7 @@
       <c r="L2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>An Inspector Calls</t>
         </is>
@@ -15276,7 +15285,7 @@
       <c r="L3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>Anita and Me</t>
         </is>
@@ -15316,7 +15325,7 @@
       <c r="L4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Jane Eyre</t>
         </is>
@@ -15356,7 +15365,7 @@
       <c r="L5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Macbeth</t>
         </is>
@@ -15396,7 +15405,7 @@
       <c r="L6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Much Ado About Nothing</t>
         </is>
@@ -15436,7 +15445,7 @@
       <c r="L7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Pride and Prejudice</t>
         </is>
@@ -15476,7 +15485,7 @@
       <c r="L8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>Romeo and Juliet</t>
         </is>
@@ -15516,7 +15525,7 @@
       <c r="L9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>The Merchant of Venice</t>
         </is>
@@ -15556,7 +15565,7 @@
       <c r="L10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>Animal Farm</t>
         </is>
@@ -15576,7 +15585,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E11" s="13" t="n"/>
+      <c r="E11" s="14" t="n"/>
       <c r="F11" s="2" t="n">
         <v>3</v>
       </c>
@@ -15592,7 +15601,7 @@
       <c r="L11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Blood Brothers</t>
         </is>
@@ -15607,7 +15616,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n"/>
+      <c r="D12" s="14" t="n"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15628,12 +15637,12 @@
       <c r="L12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="13" t="inlineStr">
         <is>
           <t>Dr Jekyll and Mr Hyde</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n"/>
+      <c r="B13" s="14" t="n"/>
       <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15664,7 +15673,7 @@
       <c r="L13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>Great Expectations</t>
         </is>
@@ -15684,7 +15693,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E14" s="13" t="n"/>
+      <c r="E14" s="14" t="n"/>
       <c r="F14" s="2" t="n">
         <v>3</v>
       </c>
@@ -15700,7 +15709,7 @@
       <c r="L14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="13" t="inlineStr">
         <is>
           <t>Lord of the Flies</t>
         </is>
@@ -15715,7 +15724,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n"/>
+      <c r="D15" s="14" t="n"/>
       <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15736,7 +15745,7 @@
       <c r="L15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Unseen Poetry</t>
         </is>
@@ -15746,7 +15755,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n"/>
+      <c r="C16" s="14" t="n"/>
       <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15772,7 +15781,7 @@
       <c r="L16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>A Taste of Honey</t>
         </is>
@@ -15782,8 +15791,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C17" s="13" t="n"/>
-      <c r="D17" s="13" t="n"/>
+      <c r="C17" s="14" t="n"/>
+      <c r="D17" s="14" t="n"/>
       <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15804,7 +15813,7 @@
       <c r="L17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>DNA</t>
         </is>
@@ -15814,13 +15823,13 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C18" s="13" t="n"/>
+      <c r="C18" s="14" t="n"/>
       <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E18" s="13" t="n"/>
+      <c r="E18" s="14" t="n"/>
       <c r="F18" s="2" t="n">
         <v>2</v>
       </c>
@@ -15836,7 +15845,7 @@
       <c r="L18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="inlineStr">
+      <c r="A19" s="13" t="inlineStr">
         <is>
           <t>Frankenstein</t>
         </is>
@@ -15851,8 +15860,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n"/>
-      <c r="E19" s="13" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
       <c r="F19" s="2" t="n">
         <v>2</v>
       </c>
@@ -15868,7 +15877,7 @@
       <c r="L19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Leave Taking</t>
         </is>
@@ -15878,13 +15887,13 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C20" s="13" t="n"/>
+      <c r="C20" s="14" t="n"/>
       <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E20" s="13" t="n"/>
+      <c r="E20" s="14" t="n"/>
       <c r="F20" s="2" t="n">
         <v>2</v>
       </c>
@@ -15900,13 +15909,13 @@
       <c r="L20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="inlineStr">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>Never Let Me Go</t>
         </is>
       </c>
-      <c r="B21" s="13" t="n"/>
-      <c r="C21" s="13" t="n"/>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
       <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15932,12 +15941,12 @@
       <c r="L21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>Poetry: Conflict</t>
         </is>
       </c>
-      <c r="B22" s="13" t="n"/>
+      <c r="B22" s="14" t="n"/>
       <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15948,7 +15957,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="E22" s="13" t="n"/>
+      <c r="E22" s="14" t="n"/>
       <c r="F22" s="2" t="n">
         <v>2</v>
       </c>
@@ -15964,18 +15973,18 @@
       <c r="L22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Silas Marner</t>
         </is>
       </c>
-      <c r="B23" s="13" t="n"/>
+      <c r="B23" s="14" t="n"/>
       <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n"/>
+      <c r="D23" s="14" t="n"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -15996,7 +16005,7 @@
       <c r="L23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>The Tempest</t>
         </is>
@@ -16011,8 +16020,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n"/>
-      <c r="E24" s="13" t="n"/>
+      <c r="D24" s="14" t="n"/>
+      <c r="E24" s="14" t="n"/>
       <c r="F24" s="2" t="n">
         <v>2</v>
       </c>
@@ -16028,13 +16037,13 @@
       <c r="L24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>The War of the Worlds</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n"/>
-      <c r="C25" s="13" t="n"/>
+      <c r="B25" s="14" t="n"/>
+      <c r="C25" s="14" t="n"/>
       <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16060,18 +16069,18 @@
       <c r="L25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>The Woman in Black</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n"/>
+      <c r="B26" s="14" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n"/>
+      <c r="D26" s="14" t="n"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16092,19 +16101,19 @@
       <c r="L26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="inlineStr">
+      <c r="A27" s="13" t="inlineStr">
         <is>
           <t>Boys Don’t Cry</t>
         </is>
       </c>
-      <c r="B27" s="13" t="n"/>
+      <c r="B27" s="14" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n"/>
-      <c r="E27" s="13" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="14" t="n"/>
       <c r="F27" s="2" t="n">
         <v>1</v>
       </c>
@@ -16120,19 +16129,19 @@
       <c r="L27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="inlineStr">
+      <c r="A28" s="13" t="inlineStr">
         <is>
           <t>Coram Boy</t>
         </is>
       </c>
-      <c r="B28" s="13" t="n"/>
+      <c r="B28" s="14" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n"/>
-      <c r="E28" s="13" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="14" t="n"/>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
@@ -16148,14 +16157,14 @@
       <c r="L28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="inlineStr">
+      <c r="A29" s="13" t="inlineStr">
         <is>
           <t>Henry V</t>
         </is>
       </c>
-      <c r="B29" s="13" t="n"/>
-      <c r="C29" s="13" t="n"/>
-      <c r="D29" s="13" t="n"/>
+      <c r="B29" s="14" t="n"/>
+      <c r="C29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16176,19 +16185,19 @@
       <c r="L29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="inlineStr">
+      <c r="A30" s="13" t="inlineStr">
         <is>
           <t>Hobson’s Choice</t>
         </is>
       </c>
-      <c r="B30" s="13" t="n"/>
+      <c r="B30" s="14" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n"/>
-      <c r="E30" s="13" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="14" t="n"/>
       <c r="F30" s="2" t="n">
         <v>1</v>
       </c>
@@ -16204,7 +16213,7 @@
       <c r="L30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Jekyll and Hyde</t>
         </is>
@@ -16214,9 +16223,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C31" s="13" t="n"/>
-      <c r="D31" s="13" t="n"/>
-      <c r="E31" s="13" t="n"/>
+      <c r="C31" s="14" t="n"/>
+      <c r="D31" s="14" t="n"/>
+      <c r="E31" s="14" t="n"/>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
@@ -16232,19 +16241,19 @@
       <c r="L31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Journey’s End</t>
         </is>
       </c>
-      <c r="B32" s="13" t="n"/>
+      <c r="B32" s="14" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="13" t="n"/>
+      <c r="D32" s="14" t="n"/>
+      <c r="E32" s="14" t="n"/>
       <c r="F32" s="2" t="n">
         <v>1</v>
       </c>
@@ -16260,7 +16269,7 @@
       <c r="L32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="inlineStr">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Julius Caesar</t>
         </is>
@@ -16270,9 +16279,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C33" s="13" t="n"/>
-      <c r="D33" s="13" t="n"/>
-      <c r="E33" s="13" t="n"/>
+      <c r="C33" s="14" t="n"/>
+      <c r="D33" s="14" t="n"/>
+      <c r="E33" s="14" t="n"/>
       <c r="F33" s="2" t="n">
         <v>1</v>
       </c>
@@ -16288,7 +16297,7 @@
       <c r="L33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Love and Relationships Poetry</t>
         </is>
@@ -16298,9 +16307,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C34" s="13" t="n"/>
-      <c r="D34" s="13" t="n"/>
-      <c r="E34" s="13" t="n"/>
+      <c r="C34" s="14" t="n"/>
+      <c r="D34" s="14" t="n"/>
+      <c r="E34" s="14" t="n"/>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
@@ -16316,7 +16325,7 @@
       <c r="L34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>My Name is Leon</t>
         </is>
@@ -16326,9 +16335,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C35" s="13" t="n"/>
-      <c r="D35" s="13" t="n"/>
-      <c r="E35" s="13" t="n"/>
+      <c r="C35" s="14" t="n"/>
+      <c r="D35" s="14" t="n"/>
+      <c r="E35" s="14" t="n"/>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
@@ -16344,14 +16353,14 @@
       <c r="L35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+      <c r="A36" s="13" t="inlineStr">
         <is>
           <t>Oranges Are Not the Only Fruit</t>
         </is>
       </c>
-      <c r="B36" s="13" t="n"/>
-      <c r="C36" s="13" t="n"/>
-      <c r="D36" s="13" t="n"/>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="14" t="n"/>
+      <c r="D36" s="14" t="n"/>
       <c r="E36" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16372,14 +16381,14 @@
       <c r="L36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>Othello</t>
         </is>
       </c>
-      <c r="B37" s="13" t="n"/>
-      <c r="C37" s="13" t="n"/>
-      <c r="D37" s="13" t="n"/>
+      <c r="B37" s="14" t="n"/>
+      <c r="C37" s="14" t="n"/>
+      <c r="D37" s="14" t="n"/>
       <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16400,7 +16409,7 @@
       <c r="L37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="inlineStr">
+      <c r="A38" s="13" t="inlineStr">
         <is>
           <t>Pigeon English</t>
         </is>
@@ -16410,9 +16419,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C38" s="13" t="n"/>
-      <c r="D38" s="13" t="n"/>
-      <c r="E38" s="13" t="n"/>
+      <c r="C38" s="14" t="n"/>
+      <c r="D38" s="14" t="n"/>
+      <c r="E38" s="14" t="n"/>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
@@ -16428,14 +16437,14 @@
       <c r="L38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="inlineStr">
+      <c r="A39" s="13" t="inlineStr">
         <is>
           <t>Poetry Anthology</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n"/>
-      <c r="C39" s="13" t="n"/>
-      <c r="D39" s="13" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
       <c r="E39" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16456,19 +16465,19 @@
       <c r="L39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="inlineStr">
+      <c r="A40" s="13" t="inlineStr">
         <is>
           <t>Poetry: Belonging</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n"/>
+      <c r="B40" s="14" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n"/>
-      <c r="E40" s="13" t="n"/>
+      <c r="D40" s="14" t="n"/>
+      <c r="E40" s="14" t="n"/>
       <c r="F40" s="2" t="n">
         <v>1</v>
       </c>
@@ -16484,19 +16493,19 @@
       <c r="L40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Poetry: Love and Relationships</t>
         </is>
       </c>
-      <c r="B41" s="13" t="n"/>
-      <c r="C41" s="13" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
       <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E41" s="13" t="n"/>
+      <c r="E41" s="14" t="n"/>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
@@ -16512,19 +16521,19 @@
       <c r="L41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="inlineStr">
+      <c r="A42" s="13" t="inlineStr">
         <is>
           <t>Poetry: Relationships</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n"/>
+      <c r="B42" s="14" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n"/>
-      <c r="E42" s="13" t="n"/>
+      <c r="D42" s="14" t="n"/>
+      <c r="E42" s="14" t="n"/>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
@@ -16540,19 +16549,19 @@
       <c r="L42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="inlineStr">
+      <c r="A43" s="13" t="inlineStr">
         <is>
           <t>Poetry: Time and Place</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n"/>
+      <c r="B43" s="14" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n"/>
-      <c r="E43" s="13" t="n"/>
+      <c r="D43" s="14" t="n"/>
+      <c r="E43" s="14" t="n"/>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
@@ -16568,19 +16577,19 @@
       <c r="L43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="12" t="inlineStr">
+      <c r="A44" s="13" t="inlineStr">
         <is>
           <t>Poetry: Youth and Age</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n"/>
-      <c r="C44" s="13" t="n"/>
+      <c r="B44" s="14" t="n"/>
+      <c r="C44" s="14" t="n"/>
       <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="E44" s="13" t="n"/>
+      <c r="E44" s="14" t="n"/>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
@@ -16596,7 +16605,7 @@
       <c r="L44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="12" t="inlineStr">
+      <c r="A45" s="13" t="inlineStr">
         <is>
           <t>Power &amp; Conflict Poetry</t>
         </is>
@@ -16606,9 +16615,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C45" s="13" t="n"/>
-      <c r="D45" s="13" t="n"/>
-      <c r="E45" s="13" t="n"/>
+      <c r="C45" s="14" t="n"/>
+      <c r="D45" s="14" t="n"/>
+      <c r="E45" s="14" t="n"/>
       <c r="F45" s="2" t="n">
         <v>1</v>
       </c>
@@ -16624,7 +16633,7 @@
       <c r="L45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="12" t="inlineStr">
+      <c r="A46" s="13" t="inlineStr">
         <is>
           <t>Princess &amp; The Hustler</t>
         </is>
@@ -16634,9 +16643,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C46" s="13" t="n"/>
-      <c r="D46" s="13" t="n"/>
-      <c r="E46" s="13" t="n"/>
+      <c r="C46" s="14" t="n"/>
+      <c r="D46" s="14" t="n"/>
+      <c r="E46" s="14" t="n"/>
       <c r="F46" s="2" t="n">
         <v>1</v>
       </c>
@@ -16652,19 +16661,19 @@
       <c r="L46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="12" t="inlineStr">
+      <c r="A47" s="13" t="inlineStr">
         <is>
           <t>Refugee Boy</t>
         </is>
       </c>
-      <c r="B47" s="13" t="n"/>
+      <c r="B47" s="14" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n"/>
-      <c r="E47" s="13" t="n"/>
+      <c r="D47" s="14" t="n"/>
+      <c r="E47" s="14" t="n"/>
       <c r="F47" s="2" t="n">
         <v>1</v>
       </c>
@@ -16680,14 +16689,14 @@
       <c r="L47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>The Curious Incident of the Dog in the Night-Time</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n"/>
-      <c r="C48" s="13" t="n"/>
-      <c r="D48" s="13" t="n"/>
+      <c r="B48" s="14" t="n"/>
+      <c r="C48" s="14" t="n"/>
+      <c r="D48" s="14" t="n"/>
       <c r="E48" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16708,19 +16717,19 @@
       <c r="L48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+      <c r="A49" s="13" t="inlineStr">
         <is>
           <t>The Empress</t>
         </is>
       </c>
-      <c r="B49" s="13" t="n"/>
+      <c r="B49" s="14" t="n"/>
       <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n"/>
-      <c r="E49" s="13" t="n"/>
+      <c r="D49" s="14" t="n"/>
+      <c r="E49" s="14" t="n"/>
       <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
@@ -16736,14 +16745,14 @@
       <c r="L49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>The History Boys</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n"/>
-      <c r="C50" s="13" t="n"/>
-      <c r="D50" s="13" t="n"/>
+      <c r="B50" s="14" t="n"/>
+      <c r="C50" s="14" t="n"/>
+      <c r="D50" s="14" t="n"/>
       <c r="E50" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -16764,7 +16773,7 @@
       <c r="L50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>The Sign of Four</t>
         </is>
@@ -16774,9 +16783,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C51" s="13" t="n"/>
-      <c r="D51" s="13" t="n"/>
-      <c r="E51" s="13" t="n"/>
+      <c r="C51" s="14" t="n"/>
+      <c r="D51" s="14" t="n"/>
+      <c r="E51" s="14" t="n"/>
       <c r="F51" s="2" t="n">
         <v>1</v>
       </c>
@@ -16792,19 +16801,19 @@
       <c r="L51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="12" t="inlineStr">
+      <c r="A52" s="13" t="inlineStr">
         <is>
           <t>Twelfth Night</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n"/>
+      <c r="B52" s="14" t="n"/>
       <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n"/>
-      <c r="E52" s="13" t="n"/>
+      <c r="D52" s="14" t="n"/>
+      <c r="E52" s="14" t="n"/>
       <c r="F52" s="2" t="n">
         <v>1</v>
       </c>
@@ -16820,7 +16829,7 @@
       <c r="L52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="12" t="inlineStr">
+      <c r="A53" s="13" t="inlineStr">
         <is>
           <t>Worlds and Lives Poetry</t>
         </is>
@@ -16830,9 +16839,9 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="C53" s="13" t="n"/>
-      <c r="D53" s="13" t="n"/>
-      <c r="E53" s="13" t="n"/>
+      <c r="C53" s="14" t="n"/>
+      <c r="D53" s="14" t="n"/>
+      <c r="E53" s="14" t="n"/>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
@@ -16933,7 +16942,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Cell Structure and Microscopy</t>
         </is>
@@ -16943,7 +16952,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -16965,7 +16974,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Cell Division and Transport</t>
         </is>
@@ -16975,7 +16984,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
@@ -16997,7 +17006,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Organisation and the Digestive System</t>
         </is>
@@ -17029,7 +17038,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>The Heart, Blood and Circulatory Disease</t>
         </is>
@@ -17061,7 +17070,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Health, Non-Communicable Diseases and Plant Tissues</t>
         </is>
@@ -17093,7 +17102,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Communicable Diseases and Human Defences</t>
         </is>
@@ -17125,7 +17134,7 @@
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Vaccination, Antibiotics and Drug Development</t>
         </is>
@@ -17157,7 +17166,7 @@
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Photosynthesis and Respiration</t>
         </is>
@@ -17189,7 +17198,7 @@
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Culturing Microorganisms and Plant Disease</t>
         </is>
@@ -17221,7 +17230,7 @@
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Monoclonal Antibodies</t>
         </is>
@@ -17253,7 +17262,7 @@
       <c r="D12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Homeostasis and the Nervous System</t>
         </is>
@@ -17285,7 +17294,7 @@
       <c r="D13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>The Endocrine System and Blood Glucose Control</t>
         </is>
@@ -17317,7 +17326,7 @@
       <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Hormones in Reproduction and Contraception</t>
         </is>
@@ -17349,7 +17358,7 @@
       <c r="D15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Reproduction, Meiosis and DNA</t>
         </is>
@@ -17381,7 +17390,7 @@
       <c r="D16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Genetic Inheritance and Inherited Disorders</t>
         </is>
@@ -17413,7 +17422,7 @@
       <c r="D17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Variation, Evolution and Natural Selection</t>
         </is>
@@ -17445,7 +17454,7 @@
       <c r="D18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Genetic Engineering and Ecology</t>
         </is>
@@ -17477,7 +17486,7 @@
       <c r="D19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Ecosystems, Biodiversity and Human Impact</t>
         </is>
@@ -17509,7 +17518,7 @@
       <c r="D20" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>The Brain, the Eye and Temperature Control</t>
         </is>
@@ -17541,7 +17550,7 @@
       <c r="D21" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>The Kidney, Water Balance and Plant Hormones</t>
         </is>
@@ -17573,7 +17582,7 @@
       <c r="D22" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>DNA Structure, Cloning and the History of Genetics</t>
         </is>
@@ -17605,7 +17614,7 @@
       <c r="D23" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Trophic Levels and Transfer of Biomass</t>
         </is>
@@ -17637,7 +17646,7 @@
       <c r="D24" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Decomposition, Food Security and Biotechnology</t>
         </is>
@@ -17669,7 +17678,7 @@
       <c r="D25" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Atoms, Elements, Compounds and the Model of the Atom</t>
         </is>
@@ -17701,7 +17710,7 @@
       <c r="D26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>The Periodic Table and Its Groups</t>
         </is>
@@ -17733,7 +17742,7 @@
       <c r="D27" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Ionic, Covalent and Metallic Bonding</t>
         </is>
@@ -17765,7 +17774,7 @@
       <c r="D28" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Structure, Properties and Carbon Allotropes</t>
         </is>
@@ -17797,7 +17806,7 @@
       <c r="D29" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Quantitative Chemistry: Mass, Moles and Concentrations</t>
         </is>
@@ -17829,7 +17838,7 @@
       <c r="D30" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Reactivity of Metals and Metal Extraction</t>
         </is>
@@ -17861,7 +17870,7 @@
       <c r="D31" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Reactions of Acids, pH and Neutralisation</t>
         </is>
@@ -17893,7 +17902,7 @@
       <c r="D32" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Electrolysis</t>
         </is>
@@ -17925,7 +17934,7 @@
       <c r="D33" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Energy Changes in Chemical Reactions</t>
         </is>
@@ -17957,7 +17966,7 @@
       <c r="D34" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Transition Metals and Nanoparticles</t>
         </is>
@@ -17989,7 +17998,7 @@
       <c r="D35" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Yield, Atom Economy, Molar Concentrations and Gas Volumes</t>
         </is>
@@ -18021,7 +18030,7 @@
       <c r="D36" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Titrations, Chemical Cells and Fuel Cells</t>
         </is>
@@ -18053,7 +18062,7 @@
       <c r="D37" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Rates of Reaction and Collision Theory</t>
         </is>
@@ -18085,7 +18094,7 @@
       <c r="D38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Reversible Reactions and Equilibrium</t>
         </is>
@@ -18117,7 +18126,7 @@
       <c r="D39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Crude Oil, Hydrocarbons and Cracking</t>
         </is>
@@ -18149,7 +18158,7 @@
       <c r="D40" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Chemical Analysis: Purity, Chromatography and Gas Tests</t>
         </is>
@@ -18181,7 +18190,7 @@
       <c r="D41" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>The Earth's Atmosphere and Greenhouse Effect</t>
         </is>
@@ -18213,7 +18222,7 @@
       <c r="D42" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Atmospheric Pollutants and Their Effects</t>
         </is>
@@ -18245,7 +18254,7 @@
       <c r="D43" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Using Earth's Resources and Sustainability</t>
         </is>
@@ -18277,7 +18286,7 @@
       <c r="D44" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Alkenes, Alcohols and Carboxylic Acids</t>
         </is>
@@ -18309,7 +18318,7 @@
       <c r="D45" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Polymers: Addition, Condensation and Natural</t>
         </is>
@@ -18341,7 +18350,7 @@
       <c r="D46" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Chemical Tests for Ions</t>
         </is>
@@ -18373,7 +18382,7 @@
       <c r="D47" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>Materials, Corrosion, Haber Process and Fertilisers</t>
         </is>
@@ -18405,7 +18414,7 @@
       <c r="D48" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>Energy Stores, Transfers and Power</t>
         </is>
@@ -18437,7 +18446,7 @@
       <c r="D49" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Conservation of Energy, Efficiency and Energy Resources</t>
         </is>
@@ -18469,7 +18478,7 @@
       <c r="D50" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Circuits: Current, Resistance and Potential Difference</t>
         </is>
@@ -18501,7 +18510,7 @@
       <c r="D51" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E51" s="12" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>Series and Parallel Circuits</t>
         </is>
@@ -18533,7 +18542,7 @@
       <c r="D52" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E52" s="12" t="inlineStr">
+      <c r="E52" s="13" t="inlineStr">
         <is>
           <t>Domestic Electricity, Power and the National Grid</t>
         </is>
@@ -18565,7 +18574,7 @@
       <c r="D53" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="13" t="inlineStr">
         <is>
           <t>Density, States of Matter and Changes of State</t>
         </is>
@@ -18597,7 +18606,7 @@
       <c r="D54" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E54" s="12" t="inlineStr">
+      <c r="E54" s="13" t="inlineStr">
         <is>
           <t>Internal Energy, Specific Heat Capacity and Latent Heat</t>
         </is>
@@ -18629,7 +18638,7 @@
       <c r="D55" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="13" t="inlineStr">
         <is>
           <t>Atomic Structure, Radioactivity and Half-Life</t>
         </is>
@@ -18661,7 +18670,7 @@
       <c r="D56" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E56" s="12" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>Static Electricity and Electric Fields</t>
         </is>
@@ -18693,7 +18702,7 @@
       <c r="D57" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E57" s="12" t="inlineStr">
+      <c r="E57" s="13" t="inlineStr">
         <is>
           <t>Gas Pressure and Pressure in Fluids</t>
         </is>
@@ -18725,7 +18734,7 @@
       <c r="D58" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E58" s="12" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>Nuclear Radiation: Uses, Fission and Fusion</t>
         </is>
@@ -18757,7 +18766,7 @@
       <c r="D59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>Forces, Gravity and Resultant Forces</t>
         </is>
@@ -18789,7 +18798,7 @@
       <c r="D60" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E60" s="12" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>Work Done, Elasticity and Hooke's Law</t>
         </is>
@@ -18821,7 +18830,7 @@
       <c r="D61" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>Speed, Velocity and Acceleration</t>
         </is>
@@ -18853,7 +18862,7 @@
       <c r="D62" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E62" s="12" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>Newton's Laws of Motion</t>
         </is>
@@ -18885,7 +18894,7 @@
       <c r="D63" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E63" s="12" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>Stopping Distances, Braking and Momentum</t>
         </is>
@@ -18917,7 +18926,7 @@
       <c r="D64" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E64" s="12" t="inlineStr">
+      <c r="E64" s="13" t="inlineStr">
         <is>
           <t>Waves: Properties and Behaviour</t>
         </is>
@@ -18949,7 +18958,7 @@
       <c r="D65" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E65" s="12" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>The Electromagnetic Spectrum</t>
         </is>
@@ -18981,7 +18990,7 @@
       <c r="D66" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>Magnets, Electromagnetism and the Motor Effect</t>
         </is>
@@ -19013,7 +19022,7 @@
       <c r="D67" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E67" s="12" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>Moments, Levers, Gears and Momentum Changes</t>
         </is>
@@ -19045,7 +19054,7 @@
       <c r="D68" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E68" s="12" t="inlineStr">
+      <c r="E68" s="13" t="inlineStr">
         <is>
           <t>Reflection, Sound Waves and Waves for Detection</t>
         </is>
@@ -19077,7 +19086,7 @@
       <c r="D69" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E69" s="12" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>Lenses, Visible Light and Black Body Radiation</t>
         </is>
@@ -19109,7 +19118,7 @@
       <c r="D70" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E70" s="12" t="inlineStr">
+      <c r="E70" s="13" t="inlineStr">
         <is>
           <t>Electromagnetic Induction and Transformers</t>
         </is>
@@ -19141,7 +19150,7 @@
       <c r="D71" s="2" t="n">
         <v>13</v>
       </c>
-      <c r="E71" s="12" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>Space Physics: The Solar System and Beyond</t>
         </is>
@@ -19173,7 +19182,7 @@
       <c r="D72" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E72" s="13" t="inlineStr">
         <is>
           <t>Cell Structure and Microscopy</t>
         </is>
@@ -19205,7 +19214,7 @@
       <c r="D73" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E73" s="13" t="inlineStr">
         <is>
           <t>Enzymes and Transport</t>
         </is>
@@ -19237,7 +19246,7 @@
       <c r="D74" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E74" s="12" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>Cell Division and Stem Cells</t>
         </is>
@@ -19269,7 +19278,7 @@
       <c r="D75" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E75" s="12" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>The Nervous System</t>
         </is>
@@ -19301,7 +19310,7 @@
       <c r="D76" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E76" s="12" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>Genetics and DNA</t>
         </is>
@@ -19333,7 +19342,7 @@
       <c r="D77" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E77" s="12" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>Evolution and Classification</t>
         </is>
@@ -19365,7 +19374,7 @@
       <c r="D78" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E78" s="12" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>Genetic Engineering</t>
         </is>
@@ -19397,7 +19406,7 @@
       <c r="D79" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E79" s="12" t="inlineStr">
+      <c r="E79" s="13" t="inlineStr">
         <is>
           <t>Health, Disease and Medicines</t>
         </is>
@@ -19429,7 +19438,7 @@
       <c r="D80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E80" s="12" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>Homeostasis &amp; the Nervous System</t>
         </is>
@@ -19461,7 +19470,7 @@
       <c r="D81" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E81" s="12" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>Hormonal Coordination &amp; the Endocrine System</t>
         </is>
@@ -19493,7 +19502,7 @@
       <c r="D82" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E82" s="12" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>Reproduction &amp; Contraception</t>
         </is>
@@ -19525,7 +19534,7 @@
       <c r="D83" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E83" s="12" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>DNA, Genes &amp; Inheritance</t>
         </is>
@@ -19557,7 +19566,7 @@
       <c r="D84" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E84" s="12" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>Variation &amp; Evolution</t>
         </is>
@@ -19589,7 +19598,7 @@
       <c r="D85" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E85" s="12" t="inlineStr">
+      <c r="E85" s="13" t="inlineStr">
         <is>
           <t>Natural Selection &amp; Classification</t>
         </is>
@@ -19621,7 +19630,7 @@
       <c r="D86" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E86" s="12" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>Ecosystems &amp; Biodiversity</t>
         </is>
@@ -19653,7 +19662,7 @@
       <c r="D87" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E87" s="12" t="inlineStr">
+      <c r="E87" s="13" t="inlineStr">
         <is>
           <t>Trophic Levels, Pyramids &amp; the Carbon Cycle</t>
         </is>
@@ -19685,7 +19694,7 @@
       <c r="D88" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E88" s="12" t="inlineStr">
+      <c r="E88" s="13" t="inlineStr">
         <is>
           <t>Atomic Structure &amp; the Periodic Table</t>
         </is>
@@ -19717,7 +19726,7 @@
       <c r="D89" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E89" s="12" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>Electronic Configuration &amp; Trends in the Periodic Table</t>
         </is>
@@ -19749,7 +19758,7 @@
       <c r="D90" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E90" s="12" t="inlineStr">
+      <c r="E90" s="13" t="inlineStr">
         <is>
           <t>Ionic Bonding &amp; Ionic Compounds</t>
         </is>
@@ -19781,7 +19790,7 @@
       <c r="D91" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E91" s="12" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>Covalent Bonding &amp; Molecular Structures</t>
         </is>
@@ -19813,7 +19822,7 @@
       <c r="D92" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E92" s="12" t="inlineStr">
+      <c r="E92" s="13" t="inlineStr">
         <is>
           <t>Metallic Bonding &amp; Properties of Materials</t>
         </is>
@@ -19845,7 +19854,7 @@
       <c r="D93" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E93" s="12" t="inlineStr">
+      <c r="E93" s="13" t="inlineStr">
         <is>
           <t>Conservation of Mass &amp; Moles</t>
         </is>
@@ -19877,7 +19886,7 @@
       <c r="D94" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E94" s="12" t="inlineStr">
+      <c r="E94" s="13" t="inlineStr">
         <is>
           <t>Acids, Bases &amp; Making Salts</t>
         </is>
@@ -19909,7 +19918,7 @@
       <c r="D95" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E95" s="12" t="inlineStr">
+      <c r="E95" s="13" t="inlineStr">
         <is>
           <t>Electrolysis &amp; Extraction of Metals</t>
         </is>
@@ -19941,7 +19950,7 @@
       <c r="D96" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E96" s="12" t="inlineStr">
+      <c r="E96" s="13" t="inlineStr">
         <is>
           <t>Rates of Reaction &amp; Collision Theory</t>
         </is>
@@ -19973,7 +19982,7 @@
       <c r="D97" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E97" s="12" t="inlineStr">
+      <c r="E97" s="13" t="inlineStr">
         <is>
           <t>Reversible Reactions &amp; Dynamic Equilibrium</t>
         </is>
@@ -20005,7 +20014,7 @@
       <c r="D98" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E98" s="12" t="inlineStr">
+      <c r="E98" s="13" t="inlineStr">
         <is>
           <t>Crude Oil, Hydrocarbons &amp; Alkanes</t>
         </is>
@@ -20037,7 +20046,7 @@
       <c r="D99" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E99" s="12" t="inlineStr">
+      <c r="E99" s="13" t="inlineStr">
         <is>
           <t>Combustion, Cracking &amp; Alkenes</t>
         </is>
@@ -20069,7 +20078,7 @@
       <c r="D100" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E100" s="12" t="inlineStr">
+      <c r="E100" s="13" t="inlineStr">
         <is>
           <t>Polymers &amp; Organic Reactions</t>
         </is>
@@ -20101,7 +20110,7 @@
       <c r="D101" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E101" s="12" t="inlineStr">
+      <c r="E101" s="13" t="inlineStr">
         <is>
           <t>Chemical Analysis &amp; Chromatography</t>
         </is>
@@ -20133,7 +20142,7 @@
       <c r="D102" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E102" s="12" t="inlineStr">
+      <c r="E102" s="13" t="inlineStr">
         <is>
           <t>Earth’s Atmosphere &amp; Climate Change</t>
         </is>
@@ -20165,7 +20174,7 @@
       <c r="D103" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E103" s="12" t="inlineStr">
+      <c r="E103" s="13" t="inlineStr">
         <is>
           <t>Using Resources &amp; Life Cycle Assessment</t>
         </is>
@@ -20197,7 +20206,7 @@
       <c r="D104" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E104" s="12" t="inlineStr">
+      <c r="E104" s="13" t="inlineStr">
         <is>
           <t>Energy Stores &amp; Transfers</t>
         </is>
@@ -20229,7 +20238,7 @@
       <c r="D105" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E105" s="12" t="inlineStr">
+      <c r="E105" s="13" t="inlineStr">
         <is>
           <t>Conservation of Energy &amp; Energy Resources</t>
         </is>
@@ -20261,7 +20270,7 @@
       <c r="D106" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E106" s="12" t="inlineStr">
+      <c r="E106" s="13" t="inlineStr">
         <is>
           <t>Current, Potential Difference &amp; Resistance</t>
         </is>
@@ -20293,7 +20302,7 @@
       <c r="D107" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E107" s="12" t="inlineStr">
+      <c r="E107" s="13" t="inlineStr">
         <is>
           <t>Series &amp; Parallel Circuits</t>
         </is>
@@ -20325,7 +20334,7 @@
       <c r="D108" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E108" s="12" t="inlineStr">
+      <c r="E108" s="13" t="inlineStr">
         <is>
           <t>Domestic Uses of Electricity &amp; Power</t>
         </is>
@@ -20357,7 +20366,7 @@
       <c r="D109" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E109" s="12" t="inlineStr">
+      <c r="E109" s="13" t="inlineStr">
         <is>
           <t>Static Electricity &amp; Electric Fields</t>
         </is>
@@ -20389,7 +20398,7 @@
       <c r="D110" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E110" s="12" t="inlineStr">
+      <c r="E110" s="13" t="inlineStr">
         <is>
           <t>Particle Model &amp; Density</t>
         </is>
@@ -20421,7 +20430,7 @@
       <c r="D111" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E111" s="12" t="inlineStr">
+      <c r="E111" s="13" t="inlineStr">
         <is>
           <t>Changes of State &amp; Internal Energy</t>
         </is>
@@ -20453,7 +20462,7 @@
       <c r="D112" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E112" s="12" t="inlineStr">
+      <c r="E112" s="13" t="inlineStr">
         <is>
           <t>Forces &amp; Newton’s Laws</t>
         </is>
@@ -20485,7 +20494,7 @@
       <c r="D113" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E113" s="12" t="inlineStr">
+      <c r="E113" s="13" t="inlineStr">
         <is>
           <t>Momentum &amp; Force-Time Graphs</t>
         </is>
@@ -20517,7 +20526,7 @@
       <c r="D114" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E114" s="12" t="inlineStr">
+      <c r="E114" s="13" t="inlineStr">
         <is>
           <t>Waves: Properties, Types &amp; the Electromagnetic Spectrum</t>
         </is>
@@ -20549,7 +20558,7 @@
       <c r="D115" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E115" s="12" t="inlineStr">
+      <c r="E115" s="13" t="inlineStr">
         <is>
           <t>Light, Reflection &amp; Refraction</t>
         </is>
@@ -20581,7 +20590,7 @@
       <c r="D116" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E116" s="12" t="inlineStr">
+      <c r="E116" s="13" t="inlineStr">
         <is>
           <t>Magnetism &amp; Electromagnets</t>
         </is>
@@ -20613,7 +20622,7 @@
       <c r="D117" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E117" s="12" t="inlineStr">
+      <c r="E117" s="13" t="inlineStr">
         <is>
           <t>The Motor Effect &amp; Electromagnetic Induction</t>
         </is>
@@ -20645,7 +20654,7 @@
       <c r="D118" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E118" s="12" t="inlineStr">
+      <c r="E118" s="13" t="inlineStr">
         <is>
           <t>Particle Model of Matter</t>
         </is>
@@ -20677,7 +20686,7 @@
       <c r="D119" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E119" s="12" t="inlineStr">
+      <c r="E119" s="13" t="inlineStr">
         <is>
           <t>Forces &amp; Matter</t>
         </is>
@@ -20709,7 +20718,7 @@
       <c r="D120" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E120" s="12" t="inlineStr">
+      <c r="E120" s="13" t="inlineStr">
         <is>
           <t>Cell Structures and Microscopy</t>
         </is>
@@ -20741,7 +20750,7 @@
       <c r="D121" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E121" s="12" t="inlineStr">
+      <c r="E121" s="13" t="inlineStr">
         <is>
           <t>Cell Chemistry and Enzymes</t>
         </is>
@@ -20773,7 +20782,7 @@
       <c r="D122" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E122" s="12" t="inlineStr">
+      <c r="E122" s="13" t="inlineStr">
         <is>
           <t>Respiration</t>
         </is>
@@ -20805,7 +20814,7 @@
       <c r="D123" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E123" s="12" t="inlineStr">
+      <c r="E123" s="13" t="inlineStr">
         <is>
           <t>Photosynthesis</t>
         </is>
@@ -20837,7 +20846,7 @@
       <c r="D124" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E124" s="12" t="inlineStr">
+      <c r="E124" s="13" t="inlineStr">
         <is>
           <t>Supplying the Cell and Challenges of Size</t>
         </is>
@@ -20869,7 +20878,7 @@
       <c r="D125" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E125" s="12" t="inlineStr">
+      <c r="E125" s="13" t="inlineStr">
         <is>
           <t>The Nervous System</t>
         </is>
@@ -20901,7 +20910,7 @@
       <c r="D126" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E126" s="12" t="inlineStr">
+      <c r="E126" s="13" t="inlineStr">
         <is>
           <t>The Endocrine System</t>
         </is>
@@ -20933,7 +20942,7 @@
       <c r="D127" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E127" s="12" t="inlineStr">
+      <c r="E127" s="13" t="inlineStr">
         <is>
           <t>Homeostasis and Reproduction</t>
         </is>
@@ -20965,7 +20974,7 @@
       <c r="D128" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E128" s="12" t="inlineStr">
+      <c r="E128" s="13" t="inlineStr">
         <is>
           <t>Ecosystems</t>
         </is>
@@ -20997,7 +21006,7 @@
       <c r="D129" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E129" s="12" t="inlineStr">
+      <c r="E129" s="13" t="inlineStr">
         <is>
           <t>Cycling Materials and Decomposition</t>
         </is>
@@ -21029,7 +21038,7 @@
       <c r="D130" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E130" s="12" t="inlineStr">
+      <c r="E130" s="13" t="inlineStr">
         <is>
           <t>Inheritance</t>
         </is>
@@ -21061,7 +21070,7 @@
       <c r="D131" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E131" s="12" t="inlineStr">
+      <c r="E131" s="13" t="inlineStr">
         <is>
           <t>Natural Selection and Evolution</t>
         </is>
@@ -21093,7 +21102,7 @@
       <c r="D132" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E132" s="12" t="inlineStr">
+      <c r="E132" s="13" t="inlineStr">
         <is>
           <t>Monitoring and Maintaining the Environment</t>
         </is>
@@ -21125,7 +21134,7 @@
       <c r="D133" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E133" s="12" t="inlineStr">
+      <c r="E133" s="13" t="inlineStr">
         <is>
           <t>Feeding the Human Race</t>
         </is>
@@ -21157,7 +21166,7 @@
       <c r="D134" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E134" s="12" t="inlineStr">
+      <c r="E134" s="13" t="inlineStr">
         <is>
           <t>Health, Disease and the Immune System</t>
         </is>
@@ -21189,7 +21198,7 @@
       <c r="D135" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E135" s="12" t="inlineStr">
+      <c r="E135" s="13" t="inlineStr">
         <is>
           <t>Non-Communicable Disease and Lifestyle</t>
         </is>
@@ -21221,7 +21230,7 @@
       <c r="D136" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E136" s="12" t="inlineStr">
+      <c r="E136" s="13" t="inlineStr">
         <is>
           <t>The Particle Model</t>
         </is>
@@ -21253,7 +21262,7 @@
       <c r="D137" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E137" s="12" t="inlineStr">
+      <c r="E137" s="13" t="inlineStr">
         <is>
           <t>Atomic Structure</t>
         </is>
@@ -21285,7 +21294,7 @@
       <c r="D138" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E138" s="12" t="inlineStr">
+      <c r="E138" s="13" t="inlineStr">
         <is>
           <t>Purity and Separating Mixtures</t>
         </is>
@@ -21317,7 +21326,7 @@
       <c r="D139" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E139" s="12" t="inlineStr">
+      <c r="E139" s="13" t="inlineStr">
         <is>
           <t>Bonding</t>
         </is>
@@ -21349,7 +21358,7 @@
       <c r="D140" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E140" s="12" t="inlineStr">
+      <c r="E140" s="13" t="inlineStr">
         <is>
           <t>Properties of Materials</t>
         </is>
@@ -21381,7 +21390,7 @@
       <c r="D141" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E141" s="12" t="inlineStr">
+      <c r="E141" s="13" t="inlineStr">
         <is>
           <t>Chemical Reactions and Equations</t>
         </is>
@@ -21413,7 +21422,7 @@
       <c r="D142" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E142" s="12" t="inlineStr">
+      <c r="E142" s="13" t="inlineStr">
         <is>
           <t>Energetics</t>
         </is>
@@ -21445,7 +21454,7 @@
       <c r="D143" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E143" s="12" t="inlineStr">
+      <c r="E143" s="13" t="inlineStr">
         <is>
           <t>Types of Chemical Reactions and Electrolysis</t>
         </is>
@@ -21477,7 +21486,7 @@
       <c r="D144" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E144" s="12" t="inlineStr">
+      <c r="E144" s="13" t="inlineStr">
         <is>
           <t>Predicting Chemical Reactions — Reactivity</t>
         </is>
@@ -21509,7 +21518,7 @@
       <c r="D145" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E145" s="12" t="inlineStr">
+      <c r="E145" s="13" t="inlineStr">
         <is>
           <t>Predicting Chemical Reactions — Groups and Trends</t>
         </is>
@@ -21541,7 +21550,7 @@
       <c r="D146" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E146" s="12" t="inlineStr">
+      <c r="E146" s="13" t="inlineStr">
         <is>
           <t>Identifying Substances</t>
         </is>
@@ -21573,7 +21582,7 @@
       <c r="D147" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E147" s="12" t="inlineStr">
+      <c r="E147" s="13" t="inlineStr">
         <is>
           <t>Rates of Reaction</t>
         </is>
@@ -21605,7 +21614,7 @@
       <c r="D148" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E148" s="12" t="inlineStr">
+      <c r="E148" s="13" t="inlineStr">
         <is>
           <t>Equilibria</t>
         </is>
@@ -21637,7 +21646,7 @@
       <c r="D149" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E149" s="12" t="inlineStr">
+      <c r="E149" s="13" t="inlineStr">
         <is>
           <t>Improving Processes and Products</t>
         </is>
@@ -21669,7 +21678,7 @@
       <c r="D150" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E150" s="12" t="inlineStr">
+      <c r="E150" s="13" t="inlineStr">
         <is>
           <t>Earth's Atmosphere and Climate</t>
         </is>
@@ -21701,7 +21710,7 @@
       <c r="D151" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E151" s="12" t="inlineStr">
+      <c r="E151" s="13" t="inlineStr">
         <is>
           <t>Earth's Resources and Sustainability</t>
         </is>
@@ -21733,7 +21742,7 @@
       <c r="D152" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E152" s="12" t="inlineStr">
+      <c r="E152" s="13" t="inlineStr">
         <is>
           <t>The Particle Model and Density</t>
         </is>
@@ -21765,7 +21774,7 @@
       <c r="D153" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E153" s="12" t="inlineStr">
+      <c r="E153" s="13" t="inlineStr">
         <is>
           <t>Changes of State and Internal Energy</t>
         </is>
@@ -21797,7 +21806,7 @@
       <c r="D154" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E154" s="12" t="inlineStr">
+      <c r="E154" s="13" t="inlineStr">
         <is>
           <t>Motion</t>
         </is>
@@ -21829,7 +21838,7 @@
       <c r="D155" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E155" s="12" t="inlineStr">
+      <c r="E155" s="13" t="inlineStr">
         <is>
           <t>Newton's Laws</t>
         </is>
@@ -21861,7 +21870,7 @@
       <c r="D156" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E156" s="12" t="inlineStr">
+      <c r="E156" s="13" t="inlineStr">
         <is>
           <t>Forces in Action</t>
         </is>
@@ -21893,7 +21902,7 @@
       <c r="D157" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E157" s="12" t="inlineStr">
+      <c r="E157" s="13" t="inlineStr">
         <is>
           <t>Static Charge and Simple Circuits</t>
         </is>
@@ -21925,7 +21934,7 @@
       <c r="D158" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E158" s="12" t="inlineStr">
+      <c r="E158" s="13" t="inlineStr">
         <is>
           <t>Domestic Electricity and Electrical Power</t>
         </is>
@@ -21957,7 +21966,7 @@
       <c r="D159" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E159" s="12" t="inlineStr">
+      <c r="E159" s="13" t="inlineStr">
         <is>
           <t>Magnets and Magnetic Fields</t>
         </is>
@@ -21989,7 +21998,7 @@
       <c r="D160" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E160" s="12" t="inlineStr">
+      <c r="E160" s="13" t="inlineStr">
         <is>
           <t>Wave Behaviour</t>
         </is>
@@ -22021,7 +22030,7 @@
       <c r="D161" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E161" s="12" t="inlineStr">
+      <c r="E161" s="13" t="inlineStr">
         <is>
           <t>The Electromagnetic Spectrum</t>
         </is>
@@ -22053,7 +22062,7 @@
       <c r="D162" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E162" s="12" t="inlineStr">
+      <c r="E162" s="13" t="inlineStr">
         <is>
           <t>Radioactivity</t>
         </is>
@@ -22085,7 +22094,7 @@
       <c r="D163" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E163" s="12" t="inlineStr">
+      <c r="E163" s="13" t="inlineStr">
         <is>
           <t>Uses and Dangers of Radiation</t>
         </is>
@@ -22117,7 +22126,7 @@
       <c r="D164" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E164" s="12" t="inlineStr">
+      <c r="E164" s="13" t="inlineStr">
         <is>
           <t>Work Done, Energy and Power</t>
         </is>
@@ -22149,7 +22158,7 @@
       <c r="D165" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E165" s="12" t="inlineStr">
+      <c r="E165" s="13" t="inlineStr">
         <is>
           <t>Energy Resources and Sustainability</t>
         </is>
@@ -22181,7 +22190,7 @@
       <c r="D166" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E166" s="12" t="inlineStr">
+      <c r="E166" s="13" t="inlineStr">
         <is>
           <t>Physics on the Move</t>
         </is>
@@ -22213,7 +22222,7 @@
       <c r="D167" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E167" s="12" t="inlineStr">
+      <c r="E167" s="13" t="inlineStr">
         <is>
           <t>Global Challenges in Physics</t>
         </is>
@@ -22312,7 +22321,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Cell Structure and Microscopy</t>
         </is>
@@ -22344,7 +22353,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Cell Division and Transport</t>
         </is>
@@ -22376,7 +22385,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Organisation and the Digestive System</t>
         </is>
@@ -22408,7 +22417,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>The Heart, Blood and Circulatory Disease</t>
         </is>
@@ -22440,7 +22449,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Health, Non-Communicable Diseases and Plant Tissues</t>
         </is>
@@ -22472,7 +22481,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Communicable Diseases and Human Defences</t>
         </is>
@@ -22504,7 +22513,7 @@
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Vaccination, Antibiotics and Drug Development</t>
         </is>
@@ -22536,7 +22545,7 @@
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Photosynthesis and Respiration</t>
         </is>
@@ -22568,7 +22577,7 @@
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Homeostasis and the Nervous System</t>
         </is>
@@ -22600,7 +22609,7 @@
       <c r="D11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>The Endocrine System and Blood Glucose Control</t>
         </is>
@@ -22632,7 +22641,7 @@
       <c r="D12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Hormones in Reproduction and Contraception</t>
         </is>
@@ -22664,7 +22673,7 @@
       <c r="D13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Reproduction, Meiosis and DNA</t>
         </is>
@@ -22696,7 +22705,7 @@
       <c r="D14" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Genetic Inheritance and Inherited Disorders</t>
         </is>
@@ -22728,7 +22737,7 @@
       <c r="D15" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Variation, Evolution and Natural Selection</t>
         </is>
@@ -22760,7 +22769,7 @@
       <c r="D16" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Genetic Engineering and Ecology</t>
         </is>
@@ -22792,7 +22801,7 @@
       <c r="D17" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Ecosystems, Biodiversity and Human Impact</t>
         </is>
@@ -22824,7 +22833,7 @@
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Atoms, Elements, Compounds and the Model of the Atom</t>
         </is>
@@ -22856,7 +22865,7 @@
       <c r="D19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>The Periodic Table and Its Groups</t>
         </is>
@@ -22888,7 +22897,7 @@
       <c r="D20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Ionic, Covalent and Metallic Bonding</t>
         </is>
@@ -22920,7 +22929,7 @@
       <c r="D21" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Structure, Properties and Carbon Allotropes</t>
         </is>
@@ -22952,7 +22961,7 @@
       <c r="D22" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Quantitative Chemistry: Mass, Moles and Concentrations</t>
         </is>
@@ -22984,7 +22993,7 @@
       <c r="D23" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Reactivity of Metals and Metal Extraction</t>
         </is>
@@ -23016,7 +23025,7 @@
       <c r="D24" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Reactions of Acids, pH and Neutralisation</t>
         </is>
@@ -23048,7 +23057,7 @@
       <c r="D25" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>Electrolysis</t>
         </is>
@@ -23080,7 +23089,7 @@
       <c r="D26" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Energy Changes in Chemical Reactions</t>
         </is>
@@ -23112,7 +23121,7 @@
       <c r="D27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Rates of Reaction and Collision Theory</t>
         </is>
@@ -23144,7 +23153,7 @@
       <c r="D28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Reversible Reactions and Equilibrium</t>
         </is>
@@ -23176,7 +23185,7 @@
       <c r="D29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Crude Oil, Hydrocarbons and Cracking</t>
         </is>
@@ -23208,7 +23217,7 @@
       <c r="D30" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Chemical Analysis: Purity, Chromatography and Gas Tests</t>
         </is>
@@ -23240,7 +23249,7 @@
       <c r="D31" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>The Earth's Atmosphere and Greenhouse Effect</t>
         </is>
@@ -23272,7 +23281,7 @@
       <c r="D32" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Atmospheric Pollutants and Their Effects</t>
         </is>
@@ -23304,7 +23313,7 @@
       <c r="D33" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>Using Earth's Resources and Sustainability</t>
         </is>
@@ -23336,7 +23345,7 @@
       <c r="D34" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Energy Stores, Transfers and Power</t>
         </is>
@@ -23368,7 +23377,7 @@
       <c r="D35" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Conservation of Energy, Efficiency and Energy Resources</t>
         </is>
@@ -23400,7 +23409,7 @@
       <c r="D36" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>Circuits: Current, Resistance and Potential Difference</t>
         </is>
@@ -23432,7 +23441,7 @@
       <c r="D37" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Series and Parallel Circuits</t>
         </is>
@@ -23464,7 +23473,7 @@
       <c r="D38" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>Domestic Electricity, Power and the National Grid</t>
         </is>
@@ -23496,7 +23505,7 @@
       <c r="D39" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E39" s="12" t="inlineStr">
+      <c r="E39" s="13" t="inlineStr">
         <is>
           <t>Density, States of Matter and Changes of State</t>
         </is>
@@ -23528,7 +23537,7 @@
       <c r="D40" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E40" s="12" t="inlineStr">
+      <c r="E40" s="13" t="inlineStr">
         <is>
           <t>Internal Energy, Specific Heat Capacity and Latent Heat</t>
         </is>
@@ -23560,7 +23569,7 @@
       <c r="D41" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E41" s="12" t="inlineStr">
+      <c r="E41" s="13" t="inlineStr">
         <is>
           <t>Atomic Structure, Radioactivity and Half-Life</t>
         </is>
@@ -23592,7 +23601,7 @@
       <c r="D42" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E42" s="12" t="inlineStr">
+      <c r="E42" s="13" t="inlineStr">
         <is>
           <t>Forces, Gravity and Resultant Forces</t>
         </is>
@@ -23624,7 +23633,7 @@
       <c r="D43" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E43" s="12" t="inlineStr">
+      <c r="E43" s="13" t="inlineStr">
         <is>
           <t>Work Done, Elasticity and Hooke's Law</t>
         </is>
@@ -23656,7 +23665,7 @@
       <c r="D44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E44" s="12" t="inlineStr">
+      <c r="E44" s="13" t="inlineStr">
         <is>
           <t>Speed, Velocity and Acceleration</t>
         </is>
@@ -23688,7 +23697,7 @@
       <c r="D45" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E45" s="12" t="inlineStr">
+      <c r="E45" s="13" t="inlineStr">
         <is>
           <t>Newton's Laws of Motion</t>
         </is>
@@ -23720,7 +23729,7 @@
       <c r="D46" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E46" s="12" t="inlineStr">
+      <c r="E46" s="13" t="inlineStr">
         <is>
           <t>Stopping Distances, Braking and Momentum</t>
         </is>
@@ -23752,7 +23761,7 @@
       <c r="D47" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E47" s="12" t="inlineStr">
+      <c r="E47" s="13" t="inlineStr">
         <is>
           <t>Waves: Properties and Behaviour</t>
         </is>
@@ -23784,7 +23793,7 @@
       <c r="D48" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E48" s="12" t="inlineStr">
+      <c r="E48" s="13" t="inlineStr">
         <is>
           <t>The Electromagnetic Spectrum</t>
         </is>
@@ -23816,7 +23825,7 @@
       <c r="D49" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E49" s="12" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>Magnets, Electromagnetism and the Motor Effect</t>
         </is>
@@ -23915,7 +23924,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Medieval Medicine: Beliefs &amp; Treatments c1250–1500</t>
         </is>
@@ -23947,7 +23956,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>The Black Death &amp; Public Health in Medieval England</t>
         </is>
@@ -23979,7 +23988,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>The Medical Renaissance c1500–1700</t>
         </is>
@@ -24011,7 +24020,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>William Harvey &amp; the Great Plague 1665</t>
         </is>
@@ -24043,7 +24052,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Jenner, Vaccination &amp; 18th-Century Medicine</t>
         </is>
@@ -24075,7 +24084,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Germ Theory: Pasteur, Koch &amp; Disease</t>
         </is>
@@ -24107,7 +24116,7 @@
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Public Health &amp; Fighting Cholera in the 19th Century</t>
         </is>
@@ -24139,7 +24148,7 @@
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Modern Medicine: The NHS &amp; Antibiotics</t>
         </is>
@@ -24171,7 +24180,7 @@
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Lung Cancer, Prevention &amp; Modern Challenges</t>
         </is>
@@ -24203,7 +24212,7 @@
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Medicine on the Western Front 1914–18</t>
         </is>
@@ -24235,7 +24244,7 @@
       <c r="D12" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>The Grand Alliance &amp; the Origins of the Cold War</t>
         </is>
@@ -24267,7 +24276,7 @@
       <c r="D13" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>The Truman Doctrine, Marshall Plan &amp; Berlin Blockade</t>
         </is>
@@ -24299,7 +24308,7 @@
       <c r="D14" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>The Arms Race &amp; the Hungarian Uprising 1956</t>
         </is>
@@ -24331,7 +24340,7 @@
       <c r="D15" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>The Berlin Wall &amp; the Cuban Missile Crisis</t>
         </is>
@@ -24363,7 +24372,7 @@
       <c r="D16" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>The Prague Spring &amp; International Reactions</t>
         </is>
@@ -24395,7 +24404,7 @@
       <c r="D17" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Détente: SALT, Helsinki &amp; the Limits of Peace</t>
         </is>
@@ -24427,7 +24436,7 @@
       <c r="D18" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>The Second Cold War: Afghanistan &amp; Reagan’s SDI</t>
         </is>
@@ -24459,7 +24468,7 @@
       <c r="D19" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Gorbachev &amp; the Collapse of the Soviet Union</t>
         </is>
@@ -24491,7 +24500,7 @@
       <c r="D20" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Anglo-Saxon Government, Economy &amp; Society</t>
         </is>
@@ -24523,7 +24532,7 @@
       <c r="D21" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>The Succession Crisis &amp; Rival Claimants</t>
         </is>
@@ -24555,7 +24564,7 @@
       <c r="D22" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Stamford Bridge &amp; the Battle of Hastings</t>
         </is>
@@ -24587,7 +24596,7 @@
       <c r="D23" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>William Establishing Control: Castles &amp; Rewards</t>
         </is>
@@ -24619,7 +24628,7 @@
       <c r="D24" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Anglo-Saxon Resistance &amp; the Harrying of the North</t>
         </is>
@@ -24651,7 +24660,7 @@
       <c r="D25" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>The Feudal System &amp; Norman Government</t>
         </is>
@@ -24683,7 +24692,7 @@
       <c r="D26" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>The Norman Church, Lanfranc &amp; the Domesday Book</t>
         </is>
@@ -24715,7 +24724,7 @@
       <c r="D27" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>The Revolt of the Earls &amp; William’s Legacy</t>
         </is>
@@ -24747,7 +24756,7 @@
       <c r="D28" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>The Origins of the Weimar Republic 1918–19</t>
         </is>
@@ -24779,7 +24788,7 @@
       <c r="D29" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Early Challenges: Versailles, Spartacists &amp; the Kapp Putsch</t>
         </is>
@@ -24811,7 +24820,7 @@
       <c r="D30" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>Crisis of 1923: Hyperinflation &amp; the Ruhr</t>
         </is>
@@ -24843,7 +24852,7 @@
       <c r="D31" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="12" t="inlineStr">
+      <c r="E31" s="13" t="inlineStr">
         <is>
           <t>Stresemann &amp; the Golden Age 1924–29</t>
         </is>
@@ -24875,7 +24884,7 @@
       <c r="D32" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E32" s="12" t="inlineStr">
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>Hitler’s Early Career &amp; the Munich Putsch 1923</t>
         </is>
@@ -24907,7 +24916,7 @@
       <c r="D33" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E33" s="12" t="inlineStr">
+      <c r="E33" s="13" t="inlineStr">
         <is>
           <t>The Growth of Nazi Support 1929–32</t>
         </is>
@@ -24939,7 +24948,7 @@
       <c r="D34" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="13" t="inlineStr">
         <is>
           <t>Hitler Becomes Chancellor 1932–33</t>
         </is>
@@ -24971,7 +24980,7 @@
       <c r="D35" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E35" s="13" t="inlineStr">
         <is>
           <t>Creating the Dictatorship: Reichstag Fire to Führer</t>
         </is>
@@ -25003,7 +25012,7 @@
       <c r="D36" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>The Nazi Police State, Propaganda &amp; Opposition</t>
         </is>
@@ -25035,7 +25044,7 @@
       <c r="D37" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E37" s="12" t="inlineStr">
+      <c r="E37" s="13" t="inlineStr">
         <is>
           <t>Life in Nazi Germany: Women, Youth &amp; Persecution</t>
         </is>
@@ -25134,7 +25143,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>The Nature of God &amp; the Trinity</t>
         </is>
@@ -25166,7 +25175,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Creation, the Afterlife &amp; Judgement</t>
         </is>
@@ -25198,7 +25207,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Incarnation, Crucifixion &amp; Resurrection</t>
         </is>
@@ -25230,7 +25239,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Sin, Salvation &amp; Atonement</t>
         </is>
@@ -25262,7 +25271,7 @@
       <c r="D6" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Worship &amp; Prayer</t>
         </is>
@@ -25294,7 +25303,7 @@
       <c r="D7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Sacraments: Baptism &amp; Holy Communion</t>
         </is>
@@ -25326,7 +25335,7 @@
       <c r="D8" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Pilgrimage &amp; Festivals</t>
         </is>
@@ -25358,7 +25367,7 @@
       <c r="D9" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Mission, Evangelism &amp; the Worldwide Church</t>
         </is>
@@ -25390,7 +25399,7 @@
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Core Beliefs: Six Articles &amp; Five Roots</t>
         </is>
@@ -25422,7 +25431,7 @@
       <c r="D11" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Tawhid, the Nature of Allah &amp; Angels</t>
         </is>
@@ -25454,7 +25463,7 @@
       <c r="D12" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Risalah, Holy Books &amp; Prophethood</t>
         </is>
@@ -25486,7 +25495,7 @@
       <c r="D13" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Al-Qadr, Akhirah &amp; the Day of Judgement</t>
         </is>
@@ -25518,7 +25527,7 @@
       <c r="D14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>The Five Pillars, Ten Obligatory Acts &amp; Shahadah</t>
         </is>
@@ -25550,7 +25559,7 @@
       <c r="D15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Salah &amp; Sawm</t>
         </is>
@@ -25582,7 +25591,7 @@
       <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Zakah &amp; Hajj</t>
         </is>
@@ -25614,7 +25623,7 @@
       <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Jihad &amp; Islamic Festivals</t>
         </is>
@@ -25646,7 +25655,7 @@
       <c r="D18" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Relationships, Marriage &amp; Divorce</t>
         </is>
@@ -25678,7 +25687,7 @@
       <c r="D19" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Families, Gender Roles &amp; Equality</t>
         </is>
@@ -25710,7 +25719,7 @@
       <c r="D20" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Contraception &amp; Same-Sex Relationships</t>
         </is>
@@ -25742,7 +25751,7 @@
       <c r="D21" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Origins of the Universe &amp; Human Life</t>
         </is>
@@ -25774,7 +25783,7 @@
       <c r="D22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>The Environment &amp; Animal Rights</t>
         </is>
@@ -25806,7 +25815,7 @@
       <c r="D23" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Abortion &amp; Euthanasia</t>
         </is>
@@ -25838,7 +25847,7 @@
       <c r="D24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Peace, Justice &amp; Forgiveness</t>
         </is>
@@ -25870,7 +25879,7 @@
       <c r="D25" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>War: Just War, Holy War &amp; Pacifism</t>
         </is>
@@ -25902,7 +25911,7 @@
       <c r="D26" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>Weapons of Mass Destruction &amp; Peacemaking</t>
         </is>
@@ -25934,7 +25943,7 @@
       <c r="D27" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="12" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>Good, Evil &amp; Reasons for Crime</t>
         </is>
@@ -25966,7 +25975,7 @@
       <c r="D28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>Punishment: Aims, Types &amp; the Death Penalty</t>
         </is>
@@ -25998,7 +26007,7 @@
       <c r="D29" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E29" s="12" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>Forgiveness &amp; Corporal Punishment</t>
         </is>
@@ -26097,7 +26106,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>CPU Architecture &amp; the Fetch-Execute Cycle</t>
         </is>
@@ -26129,7 +26138,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>CPU Performance</t>
         </is>
@@ -26161,7 +26170,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Embedded Systems</t>
         </is>
@@ -26193,7 +26202,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Primary Storage (RAM, ROM &amp; Virtual Memory)</t>
         </is>
@@ -26225,7 +26234,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Secondary Storage</t>
         </is>
@@ -26257,7 +26266,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Data Representation (Binary, Hex &amp; Character Sets)</t>
         </is>
@@ -26289,7 +26298,7 @@
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Representing Images &amp; Sound</t>
         </is>
@@ -26321,7 +26330,7 @@
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Data Compression</t>
         </is>
@@ -26353,7 +26362,7 @@
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Networks, Topologies &amp; Protocols</t>
         </is>
@@ -26385,7 +26394,7 @@
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Network Security</t>
         </is>
@@ -26417,7 +26426,7 @@
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Operating Systems &amp; Utility Software</t>
         </is>
@@ -26449,7 +26458,7 @@
       <c r="D13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Ethical, Legal, Cultural &amp; Environmental Impacts</t>
         </is>
@@ -26481,7 +26490,7 @@
       <c r="D14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Computational Thinking</t>
         </is>
@@ -26513,7 +26522,7 @@
       <c r="D15" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Designing Algorithms (Pseudocode &amp; Flowcharts)</t>
         </is>
@@ -26545,7 +26554,7 @@
       <c r="D16" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Searching Algorithms</t>
         </is>
@@ -26577,7 +26586,7 @@
       <c r="D17" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Sorting Algorithms</t>
         </is>
@@ -26609,7 +26618,7 @@
       <c r="D18" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Programming Fundamentals</t>
         </is>
@@ -26641,7 +26650,7 @@
       <c r="D19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Data Types &amp; Structures</t>
         </is>
@@ -26673,7 +26682,7 @@
       <c r="D20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Advanced Programming Techniques</t>
         </is>
@@ -26705,7 +26714,7 @@
       <c r="D21" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Defensive Design &amp; Input Validation</t>
         </is>
@@ -26737,7 +26746,7 @@
       <c r="D22" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E22" s="12" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Testing &amp; Debugging</t>
         </is>
@@ -26769,7 +26778,7 @@
       <c r="D23" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E23" s="12" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Boolean Logic &amp; Truth Tables</t>
         </is>
@@ -26801,7 +26810,7 @@
       <c r="D24" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E24" s="12" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Programming Languages &amp; IDEs</t>
         </is>
@@ -26900,7 +26909,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>New &amp; Emerging Technologies</t>
         </is>
@@ -26932,7 +26941,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Energy Generation &amp; Storage</t>
         </is>
@@ -26964,7 +26973,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Modern &amp; Smart Materials</t>
         </is>
@@ -26996,7 +27005,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Systems Approach to Designing</t>
         </is>
@@ -27028,7 +27037,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Mechanical Devices</t>
         </is>
@@ -27060,7 +27069,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Materials &amp; Their Working Properties</t>
         </is>
@@ -27092,7 +27101,7 @@
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Selecting Materials &amp; Components</t>
         </is>
@@ -27124,7 +27133,7 @@
       <c r="D9" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Forces &amp; Stresses</t>
         </is>
@@ -27156,7 +27165,7 @@
       <c r="D10" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Ecological &amp; Social Footprint</t>
         </is>
@@ -27188,7 +27197,7 @@
       <c r="D11" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Sources, Origins &amp; Life Cycle Assessment</t>
         </is>
@@ -27220,7 +27229,7 @@
       <c r="D12" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Stock Forms, Types &amp; Sizes</t>
         </is>
@@ -27252,7 +27261,7 @@
       <c r="D13" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Scales of Production</t>
         </is>
@@ -27284,7 +27293,7 @@
       <c r="D14" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Surface Treatments &amp; Finishes</t>
         </is>
@@ -27316,7 +27325,7 @@
       <c r="D15" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Investigation &amp; Research Methods</t>
         </is>
@@ -27348,7 +27357,7 @@
       <c r="D16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Environmental, Social &amp; Economic Challenges</t>
         </is>
@@ -27380,7 +27389,7 @@
       <c r="D17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="12" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>The Work of Others</t>
         </is>
@@ -27412,7 +27421,7 @@
       <c r="D18" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Design Strategies &amp; Communication</t>
         </is>
@@ -27444,7 +27453,7 @@
       <c r="D19" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Prototype Development &amp; Evaluation</t>
         </is>
@@ -27476,7 +27485,7 @@
       <c r="D20" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E20" s="12" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Tolerances &amp; Material Management</t>
         </is>
@@ -27508,7 +27517,7 @@
       <c r="D21" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E21" s="12" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Specialist Tools, Equipment &amp; Processes</t>
         </is>
@@ -27607,7 +27616,7 @@
       <c r="D2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" s="12" t="inlineStr">
+      <c r="E2" s="13" t="inlineStr">
         <is>
           <t>Defining Health &amp; Wellbeing + Physical Factors</t>
         </is>
@@ -27639,7 +27648,7 @@
       <c r="D3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>Lifestyle Factors Affecting Health</t>
         </is>
@@ -27671,7 +27680,7 @@
       <c r="D4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="E4" s="12" t="inlineStr">
+      <c r="E4" s="13" t="inlineStr">
         <is>
           <t>Social, Cultural &amp; Economic Factors</t>
         </is>
@@ -27703,7 +27712,7 @@
       <c r="D5" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="12" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>Environmental Factors &amp; Life Events</t>
         </is>
@@ -27735,7 +27744,7 @@
       <c r="D6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>Physiological Health Indicators</t>
         </is>
@@ -27767,7 +27776,7 @@
       <c r="D7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Lifestyle Indicators &amp; Guidelines</t>
         </is>
@@ -27799,7 +27808,7 @@
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>The Person-Centred Approach</t>
         </is>
@@ -27831,7 +27840,7 @@
       <c r="D9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Recommendations to Improve Health</t>
         </is>
@@ -27863,7 +27872,7 @@
       <c r="D10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Barriers &amp; Obstacles to Health</t>
         </is>
@@ -27895,7 +27904,7 @@
       <c r="D11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Human Lifespan Development</t>
         </is>
@@ -27927,7 +27936,7 @@
       <c r="D12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Life Events &amp; Coping with Change</t>
         </is>
@@ -27959,7 +27968,7 @@
       <c r="D13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Care Values, Services &amp; Skills</t>
         </is>

--- a/data/gcse-subject-tracker.xlsx
+++ b/data/gcse-subject-tracker.xlsx
@@ -5685,24 +5685,54 @@
           <t>Practice</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="6" t="inlineStr">
-        <is>
-          <t>Needs building</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
-      <c r="J88" s="2" t="inlineStr"/>
-      <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
-      <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr"/>
+      <c r="F88" s="5" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L88" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>Per-problem flag</t>
+        </is>
+      </c>
       <c r="P88" s="2" t="inlineStr"/>
       <c r="Q88" s="2" t="inlineStr"/>
       <c r="R88" s="2" t="inlineStr"/>
@@ -6341,24 +6371,54 @@
           <t>Practice</t>
         </is>
       </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="6" t="inlineStr">
-        <is>
-          <t>Needs building</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
-      <c r="J101" s="2" t="inlineStr"/>
-      <c r="K101" s="2" t="inlineStr"/>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
-      <c r="N101" s="2" t="inlineStr"/>
-      <c r="O101" s="2" t="inlineStr"/>
+      <c r="F101" s="5" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H101" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L101" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>Per-problem flag</t>
+        </is>
+      </c>
       <c r="P101" s="2" t="inlineStr"/>
       <c r="Q101" s="2" t="inlineStr"/>
       <c r="R101" s="2" t="inlineStr"/>
@@ -9157,24 +9217,54 @@
           <t>Practice</t>
         </is>
       </c>
-      <c r="F154" s="6" t="inlineStr">
-        <is>
-          <t>Not built</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="6" t="inlineStr">
-        <is>
-          <t>Needs building</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
-      <c r="J154" s="2" t="inlineStr"/>
-      <c r="K154" s="2" t="inlineStr"/>
-      <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
-      <c r="N154" s="2" t="inlineStr"/>
-      <c r="O154" s="2" t="inlineStr"/>
+      <c r="F154" s="5" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="H154" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="I154" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L154" s="5" t="inlineStr">
+        <is>
+          <t>26/26</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>Per-problem flag</t>
+        </is>
+      </c>
       <c r="P154" s="2" t="inlineStr"/>
       <c r="Q154" s="2" t="inlineStr"/>
       <c r="R154" s="2" t="inlineStr"/>
